--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-52013.69</v>
+        <v>-50385.73</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,27 +1177,27 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-52065.26</v>
+        <v>-52013.69</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,42 +1608,42 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-41875.27</v>
+        <v>-52065.26</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,42 +2039,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-36021.95</v>
+        <v>-41875.27</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,42 +2470,42 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
+          <t>-54750.59814941225</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-38674.54</v>
+        <v>-36021.95</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.78</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>735.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>780.25</t>
+          <t>771.95</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>759.12</t>
+          <t>761.14</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>651.25</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-267.06</t>
+          <t>-163.86</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.63</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>281985.0</t>
+          <t>500436.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>419290.0</t>
+          <t>462942.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>432429.0</t>
+          <t>451797.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>696544.24</t>
+          <t>687666.36</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-13139</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-61697.85522680334</t>
+          <t>-58155.80653900002</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-47753.86</v>
+        <v>-38674.54</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>185.66</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,22 +3332,22 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
@@ -3357,17 +3357,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1050.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.41</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>744.8</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>789.55</t>
+          <t>780.25</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>756.36</t>
+          <t>759.12</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>646.51</t>
+          <t>651.25</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-972.48</t>
+          <t>-267.06</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.21</t>
+          <t>-103.63</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>811293.0</t>
+          <t>281985.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>426617.6</t>
+          <t>419290.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>444428.2</t>
+          <t>432429.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>709505.24</t>
+          <t>696544.24</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-17810</t>
+          <t>-13139</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-64233.12749927216</t>
+          <t>-61697.85522680334</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-35613.35</v>
+        <v>-47753.86</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>194.46</t>
+          <t>185.66</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,42 +3763,42 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>582.0</t>
+          <t>1050.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-14.75</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-9.41</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>742.2</t>
+          <t>744.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>800.05</t>
+          <t>789.55</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>752.5</t>
+          <t>756.36</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>641.89</t>
+          <t>646.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-960.76</t>
+          <t>-972.48</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-98.27</t>
+          <t>-101.21</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>421717.0</t>
+          <t>811293.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>420928.4</t>
+          <t>426617.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>387118.0</t>
+          <t>444428.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>709717.56</t>
+          <t>709505.24</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>-17810</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-69436.72264493338</t>
+          <t>-64233.12749927216</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-73709.44</v>
+        <v>-35613.35</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>178.01</t>
+          <t>194.46</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,42 +4194,42 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>744.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>757.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>412.0</t>
+          <t>582.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>750.8</t>
+          <t>742.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>813.65</t>
+          <t>800.05</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>748.46</t>
+          <t>752.5</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>637.92</t>
+          <t>641.89</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-308.26</t>
+          <t>-960.76</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-11.00</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-94.13</t>
+          <t>-98.27</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>299279.0</t>
+          <t>421717.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>445200.8</t>
+          <t>420928.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>390301.9</t>
+          <t>387118.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>708135.86</t>
+          <t>709717.56</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>54898</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-68659.86428072592</t>
+          <t>-69436.72264493338</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-83759.66</v>
+        <v>-73709.44</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.01</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
           <t>744.0</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>754.0</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>709.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>412.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.59</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>754.6</t>
+          <t>750.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>826.4</t>
+          <t>813.65</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>743.7</t>
+          <t>748.46</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>633.74</t>
+          <t>637.92</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-171.67</t>
+          <t>-308.26</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-6.70</t>
+          <t>-11.00</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-89.60</t>
+          <t>-94.13</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>282176.0</t>
+          <t>299279.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>440653.6</t>
+          <t>445200.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>416013.2</t>
+          <t>390301.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>712407.32</t>
+          <t>708135.86</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>54898</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-65914.4463804971</t>
+          <t>-68659.86428072592</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-82007.34</v>
+        <v>-83759.66</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>184.13</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>744.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>754.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>709.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>768.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-12.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>754.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>836.45</t>
+          <t>826.4</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>743.7</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>629.3</t>
+          <t>633.74</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-128.95</t>
+          <t>-171.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-6.70</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-85.14</t>
+          <t>-89.60</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>318623.0</t>
+          <t>282176.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>445568.0</t>
+          <t>440653.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>448611.4</t>
+          <t>416013.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>716409.4</t>
+          <t>712407.32</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3043</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-62988.46483201619</t>
+          <t>-65914.4463804971</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-74742.74000000001</v>
+        <v>-82007.34</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>193.69</t>
+          <t>184.13</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>760.0</t>
+          <t>764.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>768.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-50385.73</v>
+        <v>-42925.29</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-52013.69</v>
+        <v>-50385.73</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1698,17 +1698,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-7.43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-52065.26</v>
+        <v>-52013.69</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-41875.27</v>
+        <v>-52065.26</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-36021.95</v>
+        <v>-41875.27</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-12.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
+          <t>-54750.59814941225</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-38674.54</v>
+        <v>-36021.95</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.78</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>735.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>780.25</t>
+          <t>771.95</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>759.12</t>
+          <t>761.14</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>651.25</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-267.06</t>
+          <t>-163.86</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.63</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>281985.0</t>
+          <t>500436.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>419290.0</t>
+          <t>462942.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>432429.0</t>
+          <t>451797.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>696544.24</t>
+          <t>687666.36</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-13139</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-61697.85522680334</t>
+          <t>-58155.80653900002</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-47753.86</v>
+        <v>-38674.54</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>185.66</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3788,17 +3788,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1050.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-14.75</t>
+          <t>-15.63</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.41</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>744.8</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>789.55</t>
+          <t>780.25</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>756.36</t>
+          <t>759.12</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>646.51</t>
+          <t>651.25</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-972.48</t>
+          <t>-267.06</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.21</t>
+          <t>-103.63</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>811293.0</t>
+          <t>281985.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>426617.6</t>
+          <t>419290.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>444428.2</t>
+          <t>432429.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>709505.24</t>
+          <t>696544.24</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-17810</t>
+          <t>-13139</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-64233.12749927216</t>
+          <t>-61697.85522680334</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-35613.35</v>
+        <v>-47753.86</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>194.46</t>
+          <t>185.66</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>582.0</t>
+          <t>1050.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-19.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-9.41</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>742.2</t>
+          <t>744.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>800.05</t>
+          <t>789.55</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>752.5</t>
+          <t>756.36</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>641.89</t>
+          <t>646.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-960.76</t>
+          <t>-972.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-98.27</t>
+          <t>-101.21</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>421717.0</t>
+          <t>811293.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>420928.4</t>
+          <t>426617.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>387118.0</t>
+          <t>444428.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>709717.56</t>
+          <t>709505.24</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>-17810</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-69436.72264493338</t>
+          <t>-64233.12749927216</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-73709.44</v>
+        <v>-35613.35</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>178.01</t>
+          <t>194.46</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>744.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>757.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>412.0</t>
+          <t>582.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-12.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>750.8</t>
+          <t>742.2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>813.65</t>
+          <t>800.05</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>748.46</t>
+          <t>752.5</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>637.92</t>
+          <t>641.89</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-308.26</t>
+          <t>-960.76</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-11.00</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-94.13</t>
+          <t>-98.27</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>299279.0</t>
+          <t>421717.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>445200.8</t>
+          <t>420928.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>390301.9</t>
+          <t>387118.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>708135.86</t>
+          <t>709717.56</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>54898</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-68659.86428072592</t>
+          <t>-69436.72264493338</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-83759.66</v>
+        <v>-73709.44</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.01</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>744.0</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>754.0</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>709.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>412.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.59</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>754.6</t>
+          <t>750.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>826.4</t>
+          <t>813.65</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>743.7</t>
+          <t>748.46</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>633.74</t>
+          <t>637.92</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-171.67</t>
+          <t>-308.26</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-6.70</t>
+          <t>-11.00</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-89.60</t>
+          <t>-94.13</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>282176.0</t>
+          <t>299279.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>440653.6</t>
+          <t>445200.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>416013.2</t>
+          <t>390301.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>712407.32</t>
+          <t>708135.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>54898</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-65914.4463804971</t>
+          <t>-68659.86428072592</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-82007.34</v>
+        <v>-83759.66</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>184.13</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>744.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>754.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>709.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>733.3</t>
+          <t>725.65</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>772.84</t>
+          <t>773.56</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>309322.6</t>
+          <t>292951.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>677723.46</t>
+          <t>675976.12</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-42925.29</v>
+        <v>-46865.1</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-50385.73</v>
+        <v>-42925.29</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-7.43</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-52013.69</v>
+        <v>-50385.73</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-52065.26</v>
+        <v>-52013.69</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-41875.27</v>
+        <v>-52065.26</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-12.85</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-36021.95</v>
+        <v>-41875.27</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-13.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
+          <t>-54750.59814941225</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-38674.54</v>
+        <v>-36021.95</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.78</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-15.63</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>735.2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>780.25</t>
+          <t>771.95</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>759.12</t>
+          <t>761.14</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>651.25</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-267.06</t>
+          <t>-163.86</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.63</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>281985.0</t>
+          <t>500436.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>419290.0</t>
+          <t>462942.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>432429.0</t>
+          <t>451797.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>696544.24</t>
+          <t>687666.36</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-13139</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-61697.85522680334</t>
+          <t>-58155.80653900002</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-47753.86</v>
+        <v>-38674.54</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>185.66</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4219,17 +4219,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1050.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-19.2</t>
+          <t>-16.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.41</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>744.8</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>789.55</t>
+          <t>780.25</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>756.36</t>
+          <t>759.12</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>646.51</t>
+          <t>651.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-972.48</t>
+          <t>-267.06</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.21</t>
+          <t>-103.63</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>811293.0</t>
+          <t>281985.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>426617.6</t>
+          <t>419290.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>444428.2</t>
+          <t>432429.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>709505.24</t>
+          <t>696544.24</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-17810</t>
+          <t>-13139</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-64233.12749927216</t>
+          <t>-61697.85522680334</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-35613.35</v>
+        <v>-47753.86</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>194.46</t>
+          <t>185.66</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>582.0</t>
+          <t>1050.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-12.54</t>
+          <t>-20.31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-9.41</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>742.2</t>
+          <t>744.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>800.05</t>
+          <t>789.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>752.5</t>
+          <t>756.36</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>641.89</t>
+          <t>646.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-960.76</t>
+          <t>-972.48</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-98.27</t>
+          <t>-101.21</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>421717.0</t>
+          <t>811293.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>420928.4</t>
+          <t>426617.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>387118.0</t>
+          <t>444428.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>709717.56</t>
+          <t>709505.24</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>-17810</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-69436.72264493338</t>
+          <t>-64233.12749927216</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-73709.44</v>
+        <v>-35613.35</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>178.01</t>
+          <t>194.46</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>744.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>757.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>412.0</t>
+          <t>582.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>750.8</t>
+          <t>742.2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>813.65</t>
+          <t>800.05</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>748.46</t>
+          <t>752.5</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>637.92</t>
+          <t>641.89</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-308.26</t>
+          <t>-960.76</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-11.00</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-94.13</t>
+          <t>-98.27</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>299279.0</t>
+          <t>421717.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>445200.8</t>
+          <t>420928.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>390301.9</t>
+          <t>387118.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>708135.86</t>
+          <t>709717.56</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>54898</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-68659.86428072592</t>
+          <t>-69436.72264493338</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-83759.66</v>
+        <v>-73709.44</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.01</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
           <t>744.0</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>754.0</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>709.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>725.65</t>
+          <t>718.95</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>773.56</t>
+          <t>774.36</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>292951.6</t>
+          <t>296429.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>675976.12</t>
+          <t>674644.66</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-46865.1</v>
+        <v>-48147.59</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>733.3</t>
+          <t>725.65</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>772.84</t>
+          <t>773.56</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>309322.6</t>
+          <t>292951.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>677723.46</t>
+          <t>675976.12</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-42925.29</v>
+        <v>-46865.1</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-50385.73</v>
+        <v>-42925.29</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-52013.69</v>
+        <v>-50385.73</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-52065.26</v>
+        <v>-52013.69</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-41875.27</v>
+        <v>-52065.26</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-13.91</t>
+          <t>-11.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-36021.95</v>
+        <v>-41875.27</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
+          <t>-54750.59814941225</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-38674.54</v>
+        <v>-36021.95</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.78</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-16.72</t>
+          <t>-12.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>735.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>780.25</t>
+          <t>771.95</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>759.12</t>
+          <t>761.14</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>651.25</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-267.06</t>
+          <t>-163.86</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.63</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>281985.0</t>
+          <t>500436.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>419290.0</t>
+          <t>462942.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>432429.0</t>
+          <t>451797.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>696544.24</t>
+          <t>687666.36</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-13139</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-61697.85522680334</t>
+          <t>-58155.80653900002</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-47753.86</v>
+        <v>-38674.54</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>185.66</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1050.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-20.31</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.41</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>744.8</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>789.55</t>
+          <t>780.25</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>756.36</t>
+          <t>759.12</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>646.51</t>
+          <t>651.25</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-972.48</t>
+          <t>-267.06</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.21</t>
+          <t>-103.63</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>811293.0</t>
+          <t>281985.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>426617.6</t>
+          <t>419290.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>444428.2</t>
+          <t>432429.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>709505.24</t>
+          <t>696544.24</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-17810</t>
+          <t>-13139</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-64233.12749927216</t>
+          <t>-61697.85522680334</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-35613.35</v>
+        <v>-47753.86</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>194.46</t>
+          <t>185.66</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>582.0</t>
+          <t>1050.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-9.41</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>742.2</t>
+          <t>744.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>800.05</t>
+          <t>789.55</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>752.5</t>
+          <t>756.36</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>641.89</t>
+          <t>646.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-960.76</t>
+          <t>-972.48</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-98.27</t>
+          <t>-101.21</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>421717.0</t>
+          <t>811293.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>420928.4</t>
+          <t>426617.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>387118.0</t>
+          <t>444428.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>709717.56</t>
+          <t>709505.24</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>-17810</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-69436.72264493338</t>
+          <t>-64233.12749927216</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-73709.44</v>
+        <v>-35613.35</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>178.01</t>
+          <t>194.46</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>744.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>757.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>718.95</t>
+          <t>712.35</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>774.36</t>
+          <t>773.42</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>296429.4</t>
+          <t>287562.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>674644.66</t>
+          <t>664782.5</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-48147.59</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-49370.81863454734</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-46587.93819697743</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>262274</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>143.98</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>133.27</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>664.0</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>610.0</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>725.65</t>
+          <t>718.95</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>773.56</t>
+          <t>774.36</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>292951.6</t>
+          <t>296429.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>675976.12</t>
+          <t>674644.66</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-46865.1</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-49876.79689592369</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-48147.58585318638</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>245558</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>144.74</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>143.98</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>645.0</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>672.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>638.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>640.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>638.0</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>733.3</t>
+          <t>725.65</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>772.84</t>
+          <t>773.56</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>309322.6</t>
+          <t>292951.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>677723.46</t>
+          <t>675976.12</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-42925.29</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-50191.19890369411</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-46865.09729587106</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>241508</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>147.04</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>144.74</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>671.0</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>640.0</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-50385.73</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-50795.94465057103</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-42925.28873913951</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>377978</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>156.60</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>147.04</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>699.0</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>646.0</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-52013.69</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-52226.97299810403</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-50385.73048883944</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>310495</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>165.39</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>18.28</t>
-        </is>
-      </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>699.0</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>706.0</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>671.0</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-13.77</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-52065.26</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-52561.74436342486</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-52013.69261380937</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>306608</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>170.36</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>165.39</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>715.0</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>694.0</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.76</t>
+          <t>-15.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3615,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-41875.27</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-52661.39013608223</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-52065.25662755885</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>228169</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>172.66</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>170.36</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>735.0</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-36021.95</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-52769.77804672284</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-41875.26748193102</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>323363</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>178.78</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>172.66</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>739.0</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>713.0</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-12.23</t>
+          <t>-19.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-38674.54</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-54750.59814941225</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-36021.95200667955</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>438172</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>173.80</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>178.78</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>750.0</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>729.0</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-17.38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>735.2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>780.25</t>
+          <t>771.95</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>759.12</t>
+          <t>761.14</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>651.25</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-267.06</t>
+          <t>-163.86</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.63</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>281985.0</t>
+          <t>500436.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>419290.0</t>
+          <t>462942.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>432429.0</t>
+          <t>451797.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>696544.24</t>
+          <t>687666.36</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-13139</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-61697.85522680334</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-47753.86</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-58155.80653900002</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-38674.53875608178</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>500436</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>185.66</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>173.80</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>19.68</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>756.0</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>716.0</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1050.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-22.46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.41</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>744.8</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>789.55</t>
+          <t>780.25</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>756.36</t>
+          <t>759.12</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>646.51</t>
+          <t>651.25</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-972.48</t>
+          <t>-267.06</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.21</t>
+          <t>-103.63</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>811293.0</t>
+          <t>281985.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>426617.6</t>
+          <t>419290.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>444428.2</t>
+          <t>432429.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>709505.24</t>
+          <t>696544.24</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-17810</t>
+          <t>-13139</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-64233.12749927216</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-35613.35</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-61697.85522680334</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-47753.85772822483</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>281985</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>194.46</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>185.66</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>20.28</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>763.0</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>747.0</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>712.35</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>773.42</t>
+          <t>772.34</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>287562.6</t>
+          <t>252624.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>664782.5</t>
+          <t>639483.2</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>262274</v>
+        <v>135802</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>718.95</t>
+          <t>712.35</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>774.36</t>
+          <t>773.42</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>296429.4</t>
+          <t>287562.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>674644.66</t>
+          <t>664782.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>245558</v>
+        <v>262274</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>725.65</t>
+          <t>718.95</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>773.56</t>
+          <t>774.36</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>292951.6</t>
+          <t>296429.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>675976.12</t>
+          <t>674644.66</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>241508</v>
+        <v>245558</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>733.3</t>
+          <t>725.65</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>772.84</t>
+          <t>773.56</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>309322.6</t>
+          <t>292951.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>677723.46</t>
+          <t>675976.12</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>377978</v>
+        <v>241508</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>310495</v>
+        <v>377978</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-13.77</t>
+          <t>-7.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-52013.69261380937</t>
+          <t>-50385.73048883944</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>306608</v>
+        <v>310495</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-15.9</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-52065.25662755885</t>
+          <t>-52013.69261380937</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>228169</v>
+        <v>306608</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-13.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-41875.26748193102</t>
+          <t>-52065.25662755885</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>323363</v>
+        <v>228169</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-19.51</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-36021.95200667955</t>
+          <t>-41875.26748193102</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>438172</v>
+        <v>323363</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
+          <t>-54750.59814941225</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-38674.53875608178</t>
+          <t>-36021.95200667955</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>500436</v>
+        <v>438172</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.78</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-22.46</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>735.2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>780.25</t>
+          <t>771.95</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>759.12</t>
+          <t>761.14</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>651.25</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-267.06</t>
+          <t>-163.86</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.63</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>281985.0</t>
+          <t>500436.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>419290.0</t>
+          <t>462942.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>432429.0</t>
+          <t>451797.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>696544.24</t>
+          <t>687666.36</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-13139</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-61697.85522680334</t>
+          <t>-58155.80653900002</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-47753.85772822483</t>
+          <t>-38674.53875608178</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>281985</v>
+        <v>500436</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>185.66</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>701.25</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>772.34</t>
+          <t>771.56</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>252624.0</t>
+          <t>213249.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>639483.2</t>
+          <t>631907.8</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>135802</v>
+        <v>181105</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>712.35</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>773.42</t>
+          <t>772.34</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>287562.6</t>
+          <t>252624.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>664782.5</t>
+          <t>639483.2</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>262274</v>
+        <v>135802</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>718.95</t>
+          <t>712.35</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>774.36</t>
+          <t>773.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>296429.4</t>
+          <t>287562.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>674644.66</t>
+          <t>664782.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>245558</v>
+        <v>262274</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>725.65</t>
+          <t>718.95</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>773.56</t>
+          <t>774.36</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>292951.6</t>
+          <t>296429.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>675976.12</t>
+          <t>674644.66</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>241508</v>
+        <v>245558</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>733.3</t>
+          <t>725.65</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>772.84</t>
+          <t>773.56</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>309322.6</t>
+          <t>292951.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>677723.46</t>
+          <t>675976.12</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>377978</v>
+        <v>241508</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.7</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>310495</v>
+        <v>377978</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-52013.69261380937</t>
+          <t>-50385.73048883944</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>306608</v>
+        <v>310495</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-13.48</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-52065.25662755885</t>
+          <t>-52013.69261380937</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>228169</v>
+        <v>306608</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-41875.26748193102</t>
+          <t>-52065.25662755885</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>323363</v>
+        <v>228169</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-36021.95200667955</t>
+          <t>-41875.26748193102</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>438172</v>
+        <v>323363</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-13.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
+          <t>-54750.59814941225</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-38674.53875608178</t>
+          <t>-36021.95200667955</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>500436</v>
+        <v>438172</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.78</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,22 +1014,22 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>701.25</t>
+          <t>694.75</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>771.56</t>
+          <t>770.74</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>213249.4</t>
+          <t>184090.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>631907.8</t>
+          <t>625496.02</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>181105</v>
+        <v>95711</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>701.25</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>772.34</t>
+          <t>771.56</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>252624.0</t>
+          <t>213249.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>639483.2</t>
+          <t>631907.8</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>135802</v>
+        <v>181105</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>712.35</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>773.42</t>
+          <t>772.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>287562.6</t>
+          <t>252624.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>664782.5</t>
+          <t>639483.2</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>262274</v>
+        <v>135802</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>718.95</t>
+          <t>712.35</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>774.36</t>
+          <t>773.42</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>296429.4</t>
+          <t>287562.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>674644.66</t>
+          <t>664782.5</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>245558</v>
+        <v>262274</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>725.65</t>
+          <t>718.95</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>773.56</t>
+          <t>774.36</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>292951.6</t>
+          <t>296429.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>675976.12</t>
+          <t>674644.66</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>241508</v>
+        <v>245558</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>733.3</t>
+          <t>725.65</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>772.84</t>
+          <t>773.56</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>309322.6</t>
+          <t>292951.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>677723.46</t>
+          <t>675976.12</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>377978</v>
+        <v>241508</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>310495</v>
+        <v>377978</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-52013.69261380937</t>
+          <t>-50385.73048883944</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>306608</v>
+        <v>310495</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4329,17 +4329,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-52065.25662755885</t>
+          <t>-52013.69261380937</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>228169</v>
+        <v>306608</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,17 +4695,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-41875.26748193102</t>
+          <t>-52065.25662755885</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>323363</v>
+        <v>228169</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-13.91</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-36021.95200667955</t>
+          <t>-41875.26748193102</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>438172</v>
+        <v>323363</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>630.2</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>694.75</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>770.74</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>694.75</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>770.74</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>95711.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>184090.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>184090</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>238520.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>625496.02</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>625496.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-59407.18447863078</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>95711</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>95711.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>630.2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>701.25</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>771.56</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>701.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>771.5599999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>181105.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>213249.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>213249.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>261286.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>631907.8</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>631907.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-54134.00295314955</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>181105</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>181105.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>631.4</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>706.0</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>772.34</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>706</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>772.34</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>135802.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>252624.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>252624</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>286992.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>639483.2</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>639483.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-53816.8863827067</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>135802</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>135802.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>641.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>712.35</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>773.42</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>712.35</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>773.42</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>262274.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>287562.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>287562.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>323456.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>664782.5</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>664782.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-46587.93819697743</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>262274</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>262274.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>657.8</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>718.95</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>774.36</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>718.95</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>774.36</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>245558.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>296429.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>296429.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>325427.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>674644.66</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>674644.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-48147.58585318638</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>245558</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>245558.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>671.6</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>725.65</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>773.56</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>725.65</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>773.5599999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>241508.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>292951.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>292951.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>382000.7</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>675976.12</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>675976.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-46865.09729587106</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>241508</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>241508.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>686.2</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>733.3</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>772.84</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>733.3</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>772.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>377978.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>309322.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>309322.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>400021.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>677723.46</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>677723.46</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-42925.28873913951</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>377978</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>377978.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>702.8</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>740.6</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>771.72</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>740.6</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>771.72</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>310495.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>321361.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>321361.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>392151.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>673300.18</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>673300.1800000001</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-50385.73048883944</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>310495</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>310495.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>711.8</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>747.5</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>770.14</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>747.5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>770.14</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>306608.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>359349.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>359349.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>389319.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>672018.02</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>672018.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-52013.69261380937</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>306608</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>306608.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>722.4</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>754.55</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>768.06</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>754.55</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>768.0599999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>228169.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>354425.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>354425</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>390521.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>675976.46</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>675976.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-52065.25662755885</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>228169</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>228169.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>735.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>760.7</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>766.1</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>760.7</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>766.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>323363.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>471049.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>471049.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>445989.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>679269.88</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>679269.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-41875.26748193102</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>323363</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>323363.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>247.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>638.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>640.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,42 +1014,42 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1058,29 +1058,29 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN2" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-37.34</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-32.65</t>
+          <t>-33.59</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,22 +1444,22 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1469,17 +1469,17 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1488,29 +1488,29 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN3" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN5" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>718.95</v>
+        <v>712.35</v>
       </c>
       <c r="AN6" t="n">
-        <v>774.36</v>
+        <v>773.42</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>296429.4</v>
+        <v>287562.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>674644.66</v>
+        <v>664782.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>725.65</v>
+        <v>718.95</v>
       </c>
       <c r="AN7" t="n">
-        <v>773.5599999999999</v>
+        <v>774.36</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>292951.6</v>
+        <v>296429.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>675976.12</v>
+        <v>674644.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>733.3</v>
+        <v>725.65</v>
       </c>
       <c r="AN8" t="n">
-        <v>772.84</v>
+        <v>773.5599999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>309322.6</v>
+        <v>292951.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>677723.46</v>
+        <v>675976.12</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>740.6</v>
+        <v>733.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>771.72</v>
+        <v>772.84</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>321361.4</v>
+        <v>309322.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>673300.1800000001</v>
+        <v>677723.46</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>747.5</v>
+        <v>740.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>770.14</v>
+        <v>771.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>359349.6</v>
+        <v>321361.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>672018.02</v>
+        <v>673300.1800000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-52013.69261380937</t>
+          <t>-50385.73048883944</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>754.55</v>
+        <v>747.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>768.0599999999999</v>
+        <v>770.14</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>354425</v>
+        <v>359349.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>675976.46</v>
+        <v>672018.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-52065.25662755885</t>
+          <t>-52013.69261380937</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>760.7</v>
+        <v>754.55</v>
       </c>
       <c r="AN12" t="n">
-        <v>766.1</v>
+        <v>768.0599999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>471049.8</v>
+        <v>354425</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>679269.88</v>
+        <v>675976.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-41875.26748193102</t>
+          <t>-52065.25662755885</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN2" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-37.34</t>
+          <t>-34.77</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-33.59</t>
+          <t>-33.83</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,42 +1444,42 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1488,29 +1488,29 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN3" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-37.34</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-32.65</t>
+          <t>-33.59</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,22 +1874,22 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1918,29 +1918,29 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN6" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>718.95</v>
+        <v>712.35</v>
       </c>
       <c r="AN7" t="n">
-        <v>774.36</v>
+        <v>773.42</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>296429.4</v>
+        <v>287562.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>674644.66</v>
+        <v>664782.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>725.65</v>
+        <v>718.95</v>
       </c>
       <c r="AN8" t="n">
-        <v>773.5599999999999</v>
+        <v>774.36</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>292951.6</v>
+        <v>296429.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>675976.12</v>
+        <v>674644.66</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>733.3</v>
+        <v>725.65</v>
       </c>
       <c r="AN9" t="n">
-        <v>772.84</v>
+        <v>773.5599999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>309322.6</v>
+        <v>292951.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>677723.46</v>
+        <v>675976.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>740.6</v>
+        <v>733.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>771.72</v>
+        <v>772.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>321361.4</v>
+        <v>309322.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>673300.1800000001</v>
+        <v>677723.46</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>747.5</v>
+        <v>740.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>770.14</v>
+        <v>771.72</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>359349.6</v>
+        <v>321361.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>672018.02</v>
+        <v>673300.1800000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-52013.69261380937</t>
+          <t>-50385.73048883944</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>754.55</v>
+        <v>747.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>768.0599999999999</v>
+        <v>770.14</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>354425</v>
+        <v>359349.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>675976.46</v>
+        <v>672018.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-52065.25662755885</t>
+          <t>-52013.69261380937</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN2" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-34.77</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-33.83</t>
+          <t>-33.66</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN3" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-37.34</t>
+          <t>-34.77</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-33.59</t>
+          <t>-33.83</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,42 +1874,42 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1918,29 +1918,29 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN4" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-37.34</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-32.65</t>
+          <t>-33.59</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,22 +2304,22 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -2329,17 +2329,17 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2348,29 +2348,29 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN7" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>718.95</v>
+        <v>712.35</v>
       </c>
       <c r="AN8" t="n">
-        <v>774.36</v>
+        <v>773.42</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>296429.4</v>
+        <v>287562.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>674644.66</v>
+        <v>664782.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>725.65</v>
+        <v>718.95</v>
       </c>
       <c r="AN9" t="n">
-        <v>773.5599999999999</v>
+        <v>774.36</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>292951.6</v>
+        <v>296429.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>675976.12</v>
+        <v>674644.66</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>733.3</v>
+        <v>725.65</v>
       </c>
       <c r="AN10" t="n">
-        <v>772.84</v>
+        <v>773.5599999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>309322.6</v>
+        <v>292951.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>677723.46</v>
+        <v>675976.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>740.6</v>
+        <v>733.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>771.72</v>
+        <v>772.84</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>321361.4</v>
+        <v>309322.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>673300.1800000001</v>
+        <v>677723.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>747.5</v>
+        <v>740.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>770.14</v>
+        <v>771.72</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>359349.6</v>
+        <v>321361.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>672018.02</v>
+        <v>673300.1800000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-52013.69261380937</t>
+          <t>-50385.73048883944</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,274 +1014,274 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-30.84</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-33.10</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>406522.3519736843</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>55.16</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>45.09</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>15166</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AM2" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-33.00</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-33.66</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>407167.6386138613</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>54.74</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>44.93</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>15050</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-34.77</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-33.83</t>
+          <t>-33.66</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN4" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-37.34</t>
+          <t>-34.77</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-33.59</t>
+          <t>-33.83</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,42 +2304,42 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2348,29 +2348,29 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN5" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-37.34</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-32.65</t>
+          <t>-33.59</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,22 +2734,22 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,29 +2778,29 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN6" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN8" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>718.95</v>
+        <v>712.35</v>
       </c>
       <c r="AN9" t="n">
-        <v>774.36</v>
+        <v>773.42</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>296429.4</v>
+        <v>287562.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>674644.66</v>
+        <v>664782.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>725.65</v>
+        <v>718.95</v>
       </c>
       <c r="AN10" t="n">
-        <v>773.5599999999999</v>
+        <v>774.36</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>292951.6</v>
+        <v>296429.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>675976.12</v>
+        <v>674644.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>733.3</v>
+        <v>725.65</v>
       </c>
       <c r="AN11" t="n">
-        <v>772.84</v>
+        <v>773.5599999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>309322.6</v>
+        <v>292951.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>677723.46</v>
+        <v>675976.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>740.6</v>
+        <v>733.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>771.72</v>
+        <v>772.84</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>321361.4</v>
+        <v>309322.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>673300.1800000001</v>
+        <v>677723.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>646.4</t>
+          <t>661.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>675.15</v>
+        <v>674.65</v>
       </c>
       <c r="AN2" t="n">
-        <v>766.86</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>697.59</t>
+          <t>700.39</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-30.84</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-33.10</t>
+          <t>-31.20</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-136.79</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>135365.2</v>
+        <v>213263.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>174307.3</t>
+          <t>198676.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>574226.34</v>
+        <v>573003.24</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-38942</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-52374.34377918849</t>
+          <t>-47427.49449711009</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-49605.36603708362</t>
+          <t>-20219.82344567886</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>149.33</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>644.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1454,264 +1454,264 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-30.84</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-33.10</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>407575.7262295082</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>55.16</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>45.09</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>15166</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AM3" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-33.00</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-33.66</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>406522.3519736843</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>55.16</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>45.09</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>15166</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,14 +1726,14 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1884,63 +1884,63 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-34.77</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-33.83</t>
+          <t>-33.66</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2314,63 +2314,63 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN5" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-37.34</t>
+          <t>-34.77</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-33.59</t>
+          <t>-33.83</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2744,32 +2744,32 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,29 +2778,29 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN6" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-37.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-32.65</t>
+          <t>-33.59</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -3189,17 +3189,17 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3208,29 +3208,29 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN7" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3604,63 +3604,63 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4034,63 +4034,63 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN9" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,7 +4454,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>718.95</v>
+        <v>712.35</v>
       </c>
       <c r="AN10" t="n">
-        <v>774.36</v>
+        <v>773.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>296429.4</v>
+        <v>287562.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>674644.66</v>
+        <v>664782.5</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,7 +4884,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>725.65</v>
+        <v>718.95</v>
       </c>
       <c r="AN11" t="n">
-        <v>773.5599999999999</v>
+        <v>774.36</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>292951.6</v>
+        <v>296429.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>675976.12</v>
+        <v>674644.66</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,7 +5314,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>733.3</v>
+        <v>725.65</v>
       </c>
       <c r="AN12" t="n">
-        <v>772.84</v>
+        <v>773.5599999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>309322.6</v>
+        <v>292951.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>677723.46</v>
+        <v>675976.12</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>696.0</t>
+          <t>1760.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>91.85</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>661.8</t>
+          <t>684.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>674.65</v>
+        <v>673.8</v>
       </c>
       <c r="AN2" t="n">
-        <v>766.6799999999999</v>
+        <v>766.12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>700.39</t>
+          <t>703.69</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-14.80</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-31.20</t>
+          <t>-27.92</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-134.68</t>
+          <t>-131.04</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>407575.7262295082</t>
+          <t>412757.7107843137</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>213263.2</v>
+        <v>447171.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>198676.6</t>
+          <t>307005.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>573003.24</v>
+        <v>581707.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>140166</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-47427.49449711009</t>
+          <t>-30265.01427379369</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-20219.82344567886</t>
+          <t>64128.62695444649</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>187.95</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>63.71</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>733.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,17 +1444,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>646.4</t>
+          <t>661.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>675.15</v>
+        <v>674.65</v>
       </c>
       <c r="AN3" t="n">
-        <v>766.86</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>697.59</t>
+          <t>700.39</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-30.84</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-33.10</t>
+          <t>-31.20</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-136.79</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>407575.7262295082</t>
+          <t>412757.7107843137</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>135365.2</v>
+        <v>213263.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>174307.3</t>
+          <t>198676.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>574226.34</v>
+        <v>573003.24</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-38942</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52374.34377918849</t>
+          <t>-47427.49449711009</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-49605.36603708362</t>
+          <t>-20219.82344567886</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>149.33</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>63.71</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>644.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,274 +1874,274 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-30.84</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-33.10</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>412757.7107843137</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>63.71</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>17516</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AM4" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-33.00</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-33.66</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>407575.7262295082</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>55.16</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>45.09</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>15166</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-34.77</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-33.83</t>
+          <t>-33.66</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>407575.7262295082</t>
+          <t>412757.7107843137</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>63.71</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,176 +2734,176 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>-6.43</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-11.22</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>639.2</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>683.15</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>769.46</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>692.9</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-2.80</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-34.77</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-33.83</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-137.60</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>412757.7107843137</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>161450.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>146674</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>217118.3</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>615716.62</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-70444</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-52873.98683047794</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-53467.41498024913</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>161450.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>150.48</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-8.51</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-10.5</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>11.53</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>630.2</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>688.8</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>769.62</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>690.04</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-11.17</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-37.34</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-33.59</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-137.34</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>407575.7262295082</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>159302.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>166838.8</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>231634.1</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>622148.62</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-64795</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-52766.09080324681</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-56843.90693450192</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>159302.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>143.98</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
       <c r="BN6" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>63.71</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,42 +3164,42 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3208,29 +3208,29 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN7" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-37.34</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-32.65</t>
+          <t>-33.59</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>407575.7262295082</t>
+          <t>412757.7107843137</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>63.71</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,22 +3594,22 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3638,29 +3638,29 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN8" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>407575.7262295082</t>
+          <t>412757.7107843137</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>63.71</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>407575.7262295082</t>
+          <t>412757.7107843137</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>63.71</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN10" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>407575.7262295082</t>
+          <t>412757.7107843137</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>63.71</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>718.95</v>
+        <v>712.35</v>
       </c>
       <c r="AN11" t="n">
-        <v>774.36</v>
+        <v>773.42</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>407575.7262295082</t>
+          <t>412757.7107843137</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>296429.4</v>
+        <v>287562.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>674644.66</v>
+        <v>664782.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>63.71</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>725.65</v>
+        <v>718.95</v>
       </c>
       <c r="AN12" t="n">
-        <v>773.5599999999999</v>
+        <v>774.36</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>407575.7262295082</t>
+          <t>412757.7107843137</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>292951.6</v>
+        <v>296429.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>675976.12</v>
+        <v>674644.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>63.71</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>價_量;【d1】;【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1760.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>97.78</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>9.96</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
+          <t>91.88</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3.88</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>684.8</t>
+          <t>698.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>673.8</v>
+        <v>672.7</v>
       </c>
       <c r="AN2" t="n">
-        <v>766.12</v>
+        <v>765</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>703.69</t>
+          <t>706.65</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>46.99</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-14.80</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-27.92</t>
-        </is>
+          <t>59.04</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-24.33</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-131.04</t>
+          <t>-127.05</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>412757.7107843137</t>
+          <t>415826.0423452768</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>447171.2</v>
+        <v>595512.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>307005.0</t>
+          <t>371093.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>581707.48</v>
+        <v>588379.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>140166</t>
+          <t>224419</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-30265.01427379369</t>
+          <t>-11817.63491464496</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>64128.62695444649</t>
+          <t>89642.95156067307</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>187.95</t>
+          <t>177.25</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.10</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>61.34</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>733.0</t>
+          <t>764.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>696.0</t>
+          <t>1760.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,59 +1451,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>91.85</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>8.34</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-1.90</t>
-        </is>
+          <t>97.78</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.63</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>661.8</t>
+          <t>684.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>674.65</v>
+        <v>673.8</v>
       </c>
       <c r="AN3" t="n">
-        <v>766.6799999999999</v>
+        <v>766.12</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>700.39</t>
+          <t>703.69</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>24.34</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-23.61</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-31.20</t>
-        </is>
+          <t>46.99</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-27.92</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-134.68</t>
+          <t>-131.04</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>412757.7107843137</t>
+          <t>415826.0423452768</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>213263.2</v>
+        <v>447171.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>198676.6</t>
+          <t>307005.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>573003.24</v>
+        <v>581707.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>140166</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-47427.49449711009</t>
+          <t>-30265.01427379369</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-20219.82344567886</t>
+          <t>64128.62695444649</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>187.95</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>61.34</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>733.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1731,11 +1715,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>6739</t>
@@ -1743,12 +1723,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1738,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1748,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1768,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1823,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1833,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,17 +1854,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1892,56 +1872,48 @@
           <t>91.85</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-4.26</t>
-        </is>
+      <c r="AH4" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-1.9</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>646.4</t>
+          <t>661.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>675.15</v>
+        <v>674.65</v>
       </c>
       <c r="AN4" t="n">
-        <v>766.86</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>697.59</t>
+          <t>700.39</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6.83</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-30.84</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-33.10</t>
-        </is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-23.61</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-31.2</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1922,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-136.79</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1932,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>412757.7107843137</t>
+          <t>415826.0423452768</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>135365.2</v>
+        <v>213263.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>174307.3</t>
+          <t>198676.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>574226.34</v>
+        <v>573003.24</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-38942</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52374.34377918849</t>
+          <t>-47427.49449711009</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-49605.36603708362</t>
+          <t>-20219.82344567886</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1988,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>149.33</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2033,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2058,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>61.34</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2073,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2098,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>644.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2161,11 +2133,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>6739</t>
@@ -2173,12 +2141,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2156,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2166,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2186,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2241,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2251,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,274 +2272,266 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>76.04</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-5.06</t>
-        </is>
+          <t>91.85</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-4.26</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-30.84</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>415826.0423452768</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>61.34</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>46.08</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>16864</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AM5" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-33.00</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-33.66</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>412757.7107843137</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>63.71</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>17516</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2591,11 +2551,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>6739</t>
@@ -2603,12 +2559,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2574,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2584,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2604,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2659,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2669,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2690,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>60.54</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-6.43</t>
-        </is>
+          <t>76.04</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-5.06</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN6" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.80</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-34.77</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-33.83</t>
-        </is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-33.66</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2758,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2768,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>412757.7107843137</t>
+          <t>415826.0423452768</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2824,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2869,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2879,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2894,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>61.34</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2909,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2934,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +2981,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +2996,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3006,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3026,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3081,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3091,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,176 +3112,168 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>37.51</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
+          <t>60.54</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-6.43</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>-11.22</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>639.2</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>683.15</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>769.46</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>692.9</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-2.80</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-34.77</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-33.83</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-137.60</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>415826.0423452768</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>161450.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>146674</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>217118.3</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>615716.62</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-70444</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-52873.98683047794</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-53467.41498024913</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>161450.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>150.48</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-8.51</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>-10.5</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>11.53</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>630.2</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>688.8</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>769.62</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>690.04</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-11.17</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-37.34</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-33.59</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-137.34</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>412757.7107843137</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>159302.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>166838.8</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>231634.1</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>622148.62</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-64795</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-52766.09080324681</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-56843.90693450192</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>159302.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>143.98</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
       <c r="BN7" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
@@ -3351,7 +3291,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3301,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3316,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>61.34</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3331,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,12 +3356,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3371,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3403,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3418,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3428,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3448,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3503,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3513,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,42 +3534,38 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>26.42</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-9.29</t>
-        </is>
+          <t>37.51</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-8.51</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3638,30 +3574,26 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN8" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-17.45</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-38.35</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-32.65</t>
-        </is>
+          <t>-11.17</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-37.34</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-33.59</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3602,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3612,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>412757.7107843137</t>
+          <t>415826.0423452768</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3668,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3713,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3738,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>61.34</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3753,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3778,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3825,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,17 +3850,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3870,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4003,17 +3935,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,42 +3956,38 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>14.52</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-10.13</t>
-        </is>
+          <t>26.42</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-9.289999999999999</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4068,30 +3996,26 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN9" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-25.78</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-39.28</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-31.23</t>
-        </is>
+          <t>-17.45</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-38.35</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-32.65</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4024,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4034,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>412757.7107843137</t>
+          <t>415826.0423452768</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4211,12 +4135,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4226,7 +4150,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4160,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>61.34</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4175,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,17 +4200,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4247,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4262,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4272,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4292,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4347,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4357,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4378,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-10.57</t>
-        </is>
+          <t>14.52</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-10.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-36.56</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-39.90</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-29.22</t>
-        </is>
+          <t>-25.78</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-39.28</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-31.23</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4446,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4456,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>412757.7107843137</t>
+          <t>415826.0423452768</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4512,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4557,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4567,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4582,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>61.34</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4597,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4622,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4669,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4684,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4694,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4714,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4769,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4779,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4800,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-4.84</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-10.02</t>
-        </is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-10.57</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN11" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-44.55</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-38.37</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-26.55</t>
-        </is>
+          <t>-36.56</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-39.9</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-29.22</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4868,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4878,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>412757.7107843137</t>
+          <t>415826.0423452768</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4934,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4979,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +4989,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5004,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>61.34</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5019,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5044,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5091,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5106,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5116,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5136,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5191,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5201,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5222,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5332,56 +5240,48 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-3.01</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-8.51</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-10.02</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>718.95</v>
+        <v>712.35</v>
       </c>
       <c r="AN12" t="n">
-        <v>774.36</v>
+        <v>773.42</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-46.43</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-34.54</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-23.59</t>
-        </is>
+          <t>-44.55</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-38.37</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-26.55</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5290,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5300,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>412757.7107843137</t>
+          <t>415826.0423452768</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>296429.4</v>
+        <v>287562.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>674644.66</v>
+        <v>664782.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5356,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5401,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5411,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5426,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>61.34</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5441,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5466,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1188.0</t>
+          <t>382.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>91.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>3.75</v>
+        <v>0.59</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.88</v>
+        <v>5.95</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.73</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>672.7</v>
+        <v>672.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>765</v>
+        <v>762.16</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>706.65</t>
+          <t>709.39</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>59.04</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>-24.33</v>
+        <v>-20.8</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-127.05</t>
+          <t>-123.13</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>595512.6</v>
+        <v>626091.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>371093.3</t>
+          <t>384772.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>588379.48</v>
+        <v>572103.12</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>224419</t>
+          <t>241319</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-11817.63491464496</t>
+          <t>-1081.15954377422</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>89642.95156067307</t>
+          <t>57969.45499601483</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>177.25</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>724.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1760.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>91.88</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>9.960000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.63</v>
+        <v>3.88</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>684.8</t>
+          <t>698.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>673.8</v>
+        <v>672.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>766.12</v>
+        <v>765</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>703.69</t>
+          <t>706.65</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>59.04</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-14.8</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>-27.92</v>
+        <v>-24.33</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-131.04</t>
+          <t>-127.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>447171.2</v>
+        <v>595512.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>307005.0</t>
+          <t>371093.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>581707.48</v>
+        <v>588379.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>140166</t>
+          <t>224419</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-30265.01427379369</t>
+          <t>-11817.63491464496</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>64128.62695444649</t>
+          <t>89642.95156067307</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>187.95</t>
+          <t>177.25</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.10</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>733.0</t>
+          <t>764.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1715,7 +1715,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>6739</t>
@@ -1723,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>696.0</t>
+          <t>1760.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1738,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1748,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1823,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1833,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1854,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1869,51 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>91.85</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>8.34</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>661.8</t>
+          <t>684.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>674.65</v>
+        <v>673.8</v>
       </c>
       <c r="AN4" t="n">
-        <v>766.6799999999999</v>
+        <v>766.12</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>700.39</t>
+          <t>703.69</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-23.61</v>
+        <v>-14.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>-31.2</v>
+        <v>-27.92</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1922,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-134.68</t>
+          <t>-131.04</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1932,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>213263.2</v>
+        <v>447171.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>198676.6</t>
+          <t>307005.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>573003.24</v>
+        <v>581707.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>140166</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-47427.49449711009</t>
+          <t>-30265.01427379369</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-20219.82344567886</t>
+          <t>64128.62695444649</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1988,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>187.95</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2033,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2043,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2058,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2073,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2098,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>733.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2133,7 +2137,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>6739</t>
@@ -2141,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2156,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2166,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2241,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2251,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2272,17 +2280,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2291,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.87</v>
+        <v>8.34</v>
       </c>
       <c r="AI5" t="n">
-        <v>-4.26</v>
+        <v>-1.9</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>646.4</t>
+          <t>661.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>675.15</v>
+        <v>674.65</v>
       </c>
       <c r="AN5" t="n">
-        <v>766.86</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>697.59</t>
+          <t>700.39</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-30.84</v>
+        <v>-23.61</v>
       </c>
       <c r="AR5" t="n">
-        <v>-33.1</v>
+        <v>-31.2</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2340,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-136.79</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2350,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>135365.2</v>
+        <v>213263.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>174307.3</t>
+          <t>198676.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>574226.34</v>
+        <v>573003.24</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-38942</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52374.34377918849</t>
+          <t>-47427.49449711009</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-49605.36603708362</t>
+          <t>-20219.82344567886</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2406,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>149.33</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2451,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2476,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2491,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2516,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>644.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2551,7 +2559,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>6739</t>
@@ -2559,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2574,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2584,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2659,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2669,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2690,266 +2702,266 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.47</v>
+        <v>0.87</v>
       </c>
       <c r="AI6" t="n">
-        <v>-5.06</v>
+        <v>-4.26</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-30.84</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>415803.5113636364</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>60.66</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>46.32</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>16678</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AM6" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-33</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-33.66</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>415826.0423452768</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>61.34</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>46.08</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>16864</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2971,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2981,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2996,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3006,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3081,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3091,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3112,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>2.47</v>
+        <v>0.47</v>
       </c>
       <c r="AI7" t="n">
-        <v>-6.43</v>
+        <v>-5.06</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN7" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-34.77</v>
+        <v>-33</v>
       </c>
       <c r="AR7" t="n">
-        <v>-33.83</v>
+        <v>-33.66</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3180,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3190,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3246,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3291,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3301,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3316,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3331,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3356,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3403,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3418,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3428,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3503,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3513,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3534,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.24</v>
+        <v>2.47</v>
       </c>
       <c r="AI8" t="n">
-        <v>-8.51</v>
+        <v>-6.43</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-37.34</v>
+        <v>-34.77</v>
       </c>
       <c r="AR8" t="n">
-        <v>-33.59</v>
+        <v>-33.83</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3602,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3612,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3668,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3713,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3723,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3738,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3753,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3778,12 +3790,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3793,7 +3805,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3825,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3840,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3850,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3925,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3935,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3956,38 +3968,38 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AI9" t="n">
-        <v>-9.289999999999999</v>
+        <v>-8.51</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -3996,26 +4008,26 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-38.35</v>
+        <v>-37.34</v>
       </c>
       <c r="AR9" t="n">
-        <v>-32.65</v>
+        <v>-33.59</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4024,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4034,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4090,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4135,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4160,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4175,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4200,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4247,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4272,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4357,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4378,38 +4390,38 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>1.56</v>
       </c>
       <c r="AI10" t="n">
-        <v>-10.13</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4418,26 +4430,26 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN10" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-39.28</v>
+        <v>-38.35</v>
       </c>
       <c r="AR10" t="n">
-        <v>-31.23</v>
+        <v>-32.65</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4446,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4456,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4557,12 +4569,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4572,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4582,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4597,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4622,17 +4634,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4669,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4684,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4694,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4769,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4779,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4800,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AI11" t="n">
-        <v>-10.57</v>
+        <v>-10.13</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-39.9</v>
+        <v>-39.28</v>
       </c>
       <c r="AR11" t="n">
-        <v>-29.22</v>
+        <v>-31.23</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4868,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4878,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4934,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4979,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4989,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5004,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5019,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5044,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5091,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5106,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5116,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5191,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5201,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5222,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-4.84</v>
+        <v>-1.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>-10.02</v>
+        <v>-10.57</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN12" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-38.37</v>
+        <v>-39.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>-26.55</v>
+        <v>-29.22</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5290,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5300,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5356,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5401,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5411,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5426,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5441,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5466,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>382.0</t>
+          <t>498.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-10.24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1033,47 +1033,47 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.59</v>
+        <v>3.81</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.95</v>
+        <v>8.98</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.73</t>
+          <t>-11.21</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>672.75</v>
+        <v>674.45</v>
       </c>
       <c r="AN2" t="n">
-        <v>762.16</v>
+        <v>759.64</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>709.39</t>
+          <t>712.93</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>97.61</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-6.7</v>
+        <v>-0.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>-20.8</v>
+        <v>-16.72</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.13</t>
+          <t>-118.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>415803.5113636364</t>
+          <t>416234.2281553398</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>626091.6</v>
+        <v>671144.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>384772.2</t>
+          <t>403254.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>572103.12</v>
+        <v>540261.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>241319</t>
+          <t>267889</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1081.15954377422</t>
+          <t>5446.587466937765</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>57969.45499601483</t>
+          <t>41349.19602585369</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>191.78</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1198,17 +1198,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>708.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>724.0</t>
+          <t>767.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1188.0</t>
+          <t>382.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>91.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>3.75</v>
+        <v>0.59</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.88</v>
+        <v>5.95</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.73</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>672.7</v>
+        <v>672.75</v>
       </c>
       <c r="AN3" t="n">
-        <v>765</v>
+        <v>762.16</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>706.65</t>
+          <t>709.39</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>59.04</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>-24.33</v>
+        <v>-20.8</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-127.05</t>
+          <t>-123.13</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>415803.5113636364</t>
+          <t>416234.2281553398</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>595512.6</v>
+        <v>626091.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>371093.3</t>
+          <t>384772.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>588379.48</v>
+        <v>572103.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>224419</t>
+          <t>241319</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-11817.63491464496</t>
+          <t>-1081.15954377422</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>89642.95156067307</t>
+          <t>57969.45499601483</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>177.25</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>724.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1760.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>91.88</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>9.960000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.63</v>
+        <v>3.88</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>684.8</t>
+          <t>698.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>673.8</v>
+        <v>672.7</v>
       </c>
       <c r="AN4" t="n">
-        <v>766.12</v>
+        <v>765</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>703.69</t>
+          <t>706.65</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>59.04</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-14.8</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>-27.92</v>
+        <v>-24.33</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-131.04</t>
+          <t>-127.05</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>415803.5113636364</t>
+          <t>416234.2281553398</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>447171.2</v>
+        <v>595512.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>307005.0</t>
+          <t>371093.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>581707.48</v>
+        <v>588379.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>140166</t>
+          <t>224419</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-30265.01427379369</t>
+          <t>-11817.63491464496</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>64128.62695444649</t>
+          <t>89642.95156067307</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>187.95</t>
+          <t>177.25</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.10</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>733.0</t>
+          <t>764.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>696.0</t>
+          <t>1760.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2295,51 +2295,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>91.85</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>8.34</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>661.8</t>
+          <t>684.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>674.65</v>
+        <v>673.8</v>
       </c>
       <c r="AN5" t="n">
-        <v>766.6799999999999</v>
+        <v>766.12</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>700.39</t>
+          <t>703.69</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-23.61</v>
+        <v>-14.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>-31.2</v>
+        <v>-27.92</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-134.68</t>
+          <t>-131.04</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>415803.5113636364</t>
+          <t>416234.2281553398</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>213263.2</v>
+        <v>447171.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>198676.6</t>
+          <t>307005.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>573003.24</v>
+        <v>581707.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>140166</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-47427.49449711009</t>
+          <t>-30265.01427379369</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-20219.82344567886</t>
+          <t>64128.62695444649</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>187.95</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>733.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,17 +2702,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2721,47 +2721,47 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.87</v>
+        <v>8.34</v>
       </c>
       <c r="AI6" t="n">
-        <v>-4.26</v>
+        <v>-1.9</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>646.4</t>
+          <t>661.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>675.15</v>
+        <v>674.65</v>
       </c>
       <c r="AN6" t="n">
-        <v>766.86</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>697.59</t>
+          <t>700.39</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-30.84</v>
+        <v>-23.61</v>
       </c>
       <c r="AR6" t="n">
-        <v>-33.1</v>
+        <v>-31.2</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-136.79</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>415803.5113636364</t>
+          <t>416234.2281553398</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>135365.2</v>
+        <v>213263.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>174307.3</t>
+          <t>198676.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>574226.34</v>
+        <v>573003.24</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-38942</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-52374.34377918849</t>
+          <t>-47427.49449711009</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-49605.36603708362</t>
+          <t>-20219.82344567886</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>149.33</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>644.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,266 +3124,266 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.47</v>
+        <v>0.87</v>
       </c>
       <c r="AI7" t="n">
-        <v>-5.06</v>
+        <v>-4.26</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-30.84</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>416234.2281553398</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>64.55</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>46.46</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>17748</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AM7" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AQ7" t="n">
-        <v>-33</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-33.66</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>415803.5113636364</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>60.66</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>46.32</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>16678</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.47</v>
+        <v>0.47</v>
       </c>
       <c r="AI8" t="n">
-        <v>-6.43</v>
+        <v>-5.06</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN8" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-34.77</v>
+        <v>-33</v>
       </c>
       <c r="AR8" t="n">
-        <v>-33.83</v>
+        <v>-33.66</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>415803.5113636364</t>
+          <t>416234.2281553398</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.24</v>
+        <v>2.47</v>
       </c>
       <c r="AI9" t="n">
-        <v>-8.51</v>
+        <v>-6.43</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN9" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-37.34</v>
+        <v>-34.77</v>
       </c>
       <c r="AR9" t="n">
-        <v>-33.59</v>
+        <v>-33.83</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>415803.5113636364</t>
+          <t>416234.2281553398</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>16.38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,38 +4390,38 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AI10" t="n">
-        <v>-9.289999999999999</v>
+        <v>-8.51</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4430,26 +4430,26 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-38.35</v>
+        <v>-37.34</v>
       </c>
       <c r="AR10" t="n">
-        <v>-32.65</v>
+        <v>-33.59</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>415803.5113636364</t>
+          <t>416234.2281553398</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>16.12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,38 +4812,38 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>1.56</v>
       </c>
       <c r="AI11" t="n">
-        <v>-10.13</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4852,26 +4852,26 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN11" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-39.28</v>
+        <v>-38.35</v>
       </c>
       <c r="AR11" t="n">
-        <v>-31.23</v>
+        <v>-32.65</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>415803.5113636364</t>
+          <t>416234.2281553398</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,17 +5056,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>16.12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AI12" t="n">
-        <v>-10.57</v>
+        <v>-10.13</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-39.9</v>
+        <v>-39.28</v>
       </c>
       <c r="AR12" t="n">
-        <v>-29.22</v>
+        <v>-31.23</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>415803.5113636364</t>
+          <t>416234.2281553398</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>498.0</t>
+          <t>1893.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.24</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>89.57</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>3.81</v>
+        <v>4.65</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.98</v>
+        <v>10.36</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.21</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>748.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>674.45</v>
+        <v>677.95</v>
       </c>
       <c r="AN2" t="n">
-        <v>759.64</v>
+        <v>758.04</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>712.93</t>
+          <t>716.71</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>97.61</t>
+          <t>150.52</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.4</v>
+        <v>6.14</v>
       </c>
       <c r="AR2" t="n">
-        <v>-16.72</v>
+        <v>-12.15</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.59</t>
+          <t>-113.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>416234.2281553398</t>
+          <t>422186.0709677419</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>365930.0</t>
+          <t>1507537.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>671144.2</v>
+        <v>875611.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>403254.7</t>
+          <t>544437.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>540261.2</v>
+        <v>555489.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>267889</t>
+          <t>331174</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>5446.587466937765</t>
+          <t>22193.54475603881</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>41349.19602585369</t>
+          <t>114301.8098460946</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>365930.0</t>
+          <t>1507537.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>191.78</t>
+          <t>199.43</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>767.0</t>
+          <t>829.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>382.0</t>
+          <t>498.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-10.24</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,17 +1436,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1455,47 +1455,47 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.59</v>
+        <v>3.81</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.95</v>
+        <v>8.98</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.73</t>
+          <t>-11.21</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>672.75</v>
+        <v>674.45</v>
       </c>
       <c r="AN3" t="n">
-        <v>762.16</v>
+        <v>759.64</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>709.39</t>
+          <t>712.93</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>97.61</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-6.7</v>
+        <v>-0.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>-20.8</v>
+        <v>-16.72</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.13</t>
+          <t>-118.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>416234.2281553398</t>
+          <t>422186.0709677419</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>626091.6</v>
+        <v>671144.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>384772.2</t>
+          <t>403254.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>572103.12</v>
+        <v>540261.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>241319</t>
+          <t>267889</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1081.15954377422</t>
+          <t>5446.587466937765</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>57969.45499601483</t>
+          <t>41349.19602585369</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>191.78</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1620,17 +1620,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>708.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>724.0</t>
+          <t>767.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1188.0</t>
+          <t>382.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>91.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>3.75</v>
+        <v>0.59</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.88</v>
+        <v>5.95</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.73</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>672.7</v>
+        <v>672.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>765</v>
+        <v>762.16</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>706.65</t>
+          <t>709.39</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>59.04</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>-24.33</v>
+        <v>-20.8</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-127.05</t>
+          <t>-123.13</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>416234.2281553398</t>
+          <t>422186.0709677419</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>595512.6</v>
+        <v>626091.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>371093.3</t>
+          <t>384772.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>588379.48</v>
+        <v>572103.12</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>224419</t>
+          <t>241319</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-11817.63491464496</t>
+          <t>-1081.15954377422</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>89642.95156067307</t>
+          <t>57969.45499601483</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>177.25</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>724.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1760.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>91.88</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>9.960000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.63</v>
+        <v>3.88</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>684.8</t>
+          <t>698.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>673.8</v>
+        <v>672.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>766.12</v>
+        <v>765</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>703.69</t>
+          <t>706.65</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>59.04</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-14.8</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>-27.92</v>
+        <v>-24.33</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-131.04</t>
+          <t>-127.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>416234.2281553398</t>
+          <t>422186.0709677419</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>447171.2</v>
+        <v>595512.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>307005.0</t>
+          <t>371093.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>581707.48</v>
+        <v>588379.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>140166</t>
+          <t>224419</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-30265.01427379369</t>
+          <t>-11817.63491464496</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>64128.62695444649</t>
+          <t>89642.95156067307</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>187.95</t>
+          <t>177.25</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.10</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>733.0</t>
+          <t>764.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>696.0</t>
+          <t>1760.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2717,51 +2717,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>91.85</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>8.34</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>661.8</t>
+          <t>684.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>674.65</v>
+        <v>673.8</v>
       </c>
       <c r="AN6" t="n">
-        <v>766.6799999999999</v>
+        <v>766.12</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>700.39</t>
+          <t>703.69</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-23.61</v>
+        <v>-14.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>-31.2</v>
+        <v>-27.92</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-134.68</t>
+          <t>-131.04</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>416234.2281553398</t>
+          <t>422186.0709677419</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>213263.2</v>
+        <v>447171.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>198676.6</t>
+          <t>307005.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>573003.24</v>
+        <v>581707.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>140166</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-47427.49449711009</t>
+          <t>-30265.01427379369</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-20219.82344567886</t>
+          <t>64128.62695444649</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>187.95</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>733.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,17 +3124,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.87</v>
+        <v>8.34</v>
       </c>
       <c r="AI7" t="n">
-        <v>-4.26</v>
+        <v>-1.9</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>646.4</t>
+          <t>661.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>675.15</v>
+        <v>674.65</v>
       </c>
       <c r="AN7" t="n">
-        <v>766.86</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>697.59</t>
+          <t>700.39</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-30.84</v>
+        <v>-23.61</v>
       </c>
       <c r="AR7" t="n">
-        <v>-33.1</v>
+        <v>-31.2</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-136.79</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>416234.2281553398</t>
+          <t>422186.0709677419</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>135365.2</v>
+        <v>213263.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>174307.3</t>
+          <t>198676.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>574226.34</v>
+        <v>573003.24</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-38942</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-52374.34377918849</t>
+          <t>-47427.49449711009</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-49605.36603708362</t>
+          <t>-20219.82344567886</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>149.33</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>644.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,266 +3546,266 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.47</v>
+        <v>0.87</v>
       </c>
       <c r="AI8" t="n">
-        <v>-5.06</v>
+        <v>-4.26</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-30.84</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>422186.0709677419</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>66.24</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>46.45</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>18213</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AM8" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AQ8" t="n">
-        <v>-33</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-33.66</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>416234.2281553398</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>64.55</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>46.46</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>17748</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>17.37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2.47</v>
+        <v>0.47</v>
       </c>
       <c r="AI9" t="n">
-        <v>-6.43</v>
+        <v>-5.06</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN9" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-34.77</v>
+        <v>-33</v>
       </c>
       <c r="AR9" t="n">
-        <v>-33.83</v>
+        <v>-33.66</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>416234.2281553398</t>
+          <t>422186.0709677419</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.24</v>
+        <v>2.47</v>
       </c>
       <c r="AI10" t="n">
-        <v>-8.51</v>
+        <v>-6.43</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-37.34</v>
+        <v>-34.77</v>
       </c>
       <c r="AR10" t="n">
-        <v>-33.59</v>
+        <v>-33.83</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>416234.2281553398</t>
+          <t>422186.0709677419</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,38 +4812,38 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" t="n">
-        <v>-9.289999999999999</v>
+        <v>-8.51</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4852,26 +4852,26 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN11" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-38.35</v>
+        <v>-37.34</v>
       </c>
       <c r="AR11" t="n">
-        <v>-32.65</v>
+        <v>-33.59</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>416234.2281553398</t>
+          <t>422186.0709677419</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>18.26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,38 +5234,38 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH12" t="n">
         <v>1.56</v>
       </c>
       <c r="AI12" t="n">
-        <v>-10.13</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5274,26 +5274,26 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN12" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-39.28</v>
+        <v>-38.35</v>
       </c>
       <c r="AR12" t="n">
-        <v>-31.23</v>
+        <v>-32.65</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>416234.2281553398</t>
+          <t>422186.0709677419</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,17 +5478,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1893.0</t>
+          <t>1382.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>811.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60.83</t>
+          <t>30.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>89.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>4.65</v>
+        <v>6.74</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.36</v>
+        <v>11.22</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>748.2</t>
+          <t>759.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>677.95</v>
+        <v>683.15</v>
       </c>
       <c r="AN2" t="n">
-        <v>758.04</v>
+        <v>756.38</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>716.71</t>
+          <t>720.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>150.52</t>
+          <t>290.80</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>6.14</v>
+        <v>13.42</v>
       </c>
       <c r="AR2" t="n">
-        <v>-12.15</v>
+        <v>-7.04</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.51</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>422186.0709677419</t>
+          <t>426236.4115755627</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1507537.0</t>
+          <t>1121228.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>875611.4</v>
+        <v>834088.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>544437.3</t>
+          <t>640629.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>555489.76</v>
+        <v>559003.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>331174</t>
+          <t>193458</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>22193.54475603881</t>
+          <t>39323.44852804988</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>114301.8098460946</t>
+          <t>133537.9192741107</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1507537.0</t>
+          <t>1121228.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>199.43</t>
+          <t>210.13</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>779.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>829.0</t>
+          <t>838.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>781.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>811.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>498.0</t>
+          <t>1893.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.24</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1451,51 +1451,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>89.57</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>3.81</v>
+        <v>4.65</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.98</v>
+        <v>10.36</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.21</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>748.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>674.45</v>
+        <v>677.95</v>
       </c>
       <c r="AN3" t="n">
-        <v>759.64</v>
+        <v>758.04</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>712.93</t>
+          <t>716.71</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>97.61</t>
+          <t>150.52</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.4</v>
+        <v>6.14</v>
       </c>
       <c r="AR3" t="n">
-        <v>-16.72</v>
+        <v>-12.15</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.59</t>
+          <t>-113.51</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>422186.0709677419</t>
+          <t>426236.4115755627</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>365930.0</t>
+          <t>1507537.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>671144.2</v>
+        <v>875611.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>403254.7</t>
+          <t>544437.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>540261.2</v>
+        <v>555489.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>267889</t>
+          <t>331174</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>5446.587466937765</t>
+          <t>22193.54475603881</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>41349.19602585369</t>
+          <t>114301.8098460946</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>365930.0</t>
+          <t>1507537.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>191.78</t>
+          <t>199.43</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>767.0</t>
+          <t>829.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>382.0</t>
+          <t>498.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-10.24</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,17 +1858,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1877,47 +1877,47 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.59</v>
+        <v>3.81</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.95</v>
+        <v>8.98</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.73</t>
+          <t>-11.21</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>672.75</v>
+        <v>674.45</v>
       </c>
       <c r="AN4" t="n">
-        <v>762.16</v>
+        <v>759.64</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>709.39</t>
+          <t>712.93</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>97.61</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-6.7</v>
+        <v>-0.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>-20.8</v>
+        <v>-16.72</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.13</t>
+          <t>-118.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>422186.0709677419</t>
+          <t>426236.4115755627</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>626091.6</v>
+        <v>671144.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>384772.2</t>
+          <t>403254.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>572103.12</v>
+        <v>540261.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>241319</t>
+          <t>267889</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1081.15954377422</t>
+          <t>5446.587466937765</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>57969.45499601483</t>
+          <t>41349.19602585369</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>191.78</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>708.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>724.0</t>
+          <t>767.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1188.0</t>
+          <t>382.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>91.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>3.75</v>
+        <v>0.59</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.88</v>
+        <v>5.95</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.73</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>672.7</v>
+        <v>672.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>765</v>
+        <v>762.16</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>706.65</t>
+          <t>709.39</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>59.04</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>-24.33</v>
+        <v>-20.8</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-127.05</t>
+          <t>-123.13</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>422186.0709677419</t>
+          <t>426236.4115755627</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>595512.6</v>
+        <v>626091.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>371093.3</t>
+          <t>384772.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>588379.48</v>
+        <v>572103.12</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>224419</t>
+          <t>241319</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-11817.63491464496</t>
+          <t>-1081.15954377422</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>89642.95156067307</t>
+          <t>57969.45499601483</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>177.25</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>724.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1760.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>91.88</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>9.960000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.63</v>
+        <v>3.88</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>684.8</t>
+          <t>698.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>673.8</v>
+        <v>672.7</v>
       </c>
       <c r="AN6" t="n">
-        <v>766.12</v>
+        <v>765</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>703.69</t>
+          <t>706.65</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>59.04</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-14.8</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>-27.92</v>
+        <v>-24.33</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-131.04</t>
+          <t>-127.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>422186.0709677419</t>
+          <t>426236.4115755627</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>447171.2</v>
+        <v>595512.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>307005.0</t>
+          <t>371093.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>581707.48</v>
+        <v>588379.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>140166</t>
+          <t>224419</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-30265.01427379369</t>
+          <t>-11817.63491464496</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>64128.62695444649</t>
+          <t>89642.95156067307</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>187.95</t>
+          <t>177.25</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.10</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>733.0</t>
+          <t>764.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>696.0</t>
+          <t>1760.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>91.85</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>8.34</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>661.8</t>
+          <t>684.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>674.65</v>
+        <v>673.8</v>
       </c>
       <c r="AN7" t="n">
-        <v>766.6799999999999</v>
+        <v>766.12</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>700.39</t>
+          <t>703.69</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-23.61</v>
+        <v>-14.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>-31.2</v>
+        <v>-27.92</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-134.68</t>
+          <t>-131.04</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>422186.0709677419</t>
+          <t>426236.4115755627</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>213263.2</v>
+        <v>447171.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>198676.6</t>
+          <t>307005.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>573003.24</v>
+        <v>581707.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>140166</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-47427.49449711009</t>
+          <t>-30265.01427379369</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-20219.82344567886</t>
+          <t>64128.62695444649</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>187.95</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>733.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,17 +3546,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3565,47 +3565,47 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.87</v>
+        <v>8.34</v>
       </c>
       <c r="AI8" t="n">
-        <v>-4.26</v>
+        <v>-1.9</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>646.4</t>
+          <t>661.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>675.15</v>
+        <v>674.65</v>
       </c>
       <c r="AN8" t="n">
-        <v>766.86</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>697.59</t>
+          <t>700.39</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-30.84</v>
+        <v>-23.61</v>
       </c>
       <c r="AR8" t="n">
-        <v>-33.1</v>
+        <v>-31.2</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-136.79</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>422186.0709677419</t>
+          <t>426236.4115755627</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>135365.2</v>
+        <v>213263.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>174307.3</t>
+          <t>198676.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>574226.34</v>
+        <v>573003.24</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-38942</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52374.34377918849</t>
+          <t>-47427.49449711009</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-49605.36603708362</t>
+          <t>-20219.82344567886</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>149.33</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>644.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,266 +3968,266 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.47</v>
+        <v>0.87</v>
       </c>
       <c r="AI9" t="n">
-        <v>-5.06</v>
+        <v>-4.26</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-30.84</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>426236.4115755627</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>68.61</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>47.2</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>18865</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AM9" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AQ9" t="n">
-        <v>-33</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-33.66</v>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>422186.0709677419</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>66.24</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>46.45</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>18213</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.47</v>
+        <v>0.47</v>
       </c>
       <c r="AI10" t="n">
-        <v>-6.43</v>
+        <v>-5.06</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN10" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-34.77</v>
+        <v>-33</v>
       </c>
       <c r="AR10" t="n">
-        <v>-33.83</v>
+        <v>-33.66</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>422186.0709677419</t>
+          <t>426236.4115755627</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>2.47</v>
       </c>
       <c r="AI11" t="n">
-        <v>-8.51</v>
+        <v>-6.43</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-37.34</v>
+        <v>-34.77</v>
       </c>
       <c r="AR11" t="n">
-        <v>-33.59</v>
+        <v>-33.83</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>422186.0709677419</t>
+          <t>426236.4115755627</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,38 +5234,38 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
-        <v>-9.289999999999999</v>
+        <v>-8.51</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5274,26 +5274,26 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN12" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-38.35</v>
+        <v>-37.34</v>
       </c>
       <c r="AR12" t="n">
-        <v>-32.65</v>
+        <v>-33.59</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>422186.0709677419</t>
+          <t>426236.4115755627</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -913,7 +913,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>878.0</t>
+          <t>547.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>792.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>13.71</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,66 +1094,66 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>88.05</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>96.02</t>
+          <t>76.51</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>2.43</v>
+        <v>-3.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.38</v>
+        <v>12.81</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>773.2</t>
+          <t>781.0</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>688.05</v>
+        <v>692.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>755.04</v>
+        <v>751.28</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>724.66</t>
+          <t>727.76</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>917.69</t>
+          <t>873.82</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>17.46</v>
+        <v>17.56</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-2.14</v>
+        <v>1.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-102.37</t>
+          <t>-98.00</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>428295.7451923077</t>
+          <t>428930.0367412141</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>712499.0</t>
+          <t>417886.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>795957</v>
+        <v>825016</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>695734.8</t>
+          <t>725553.8</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>555261.3199999999</v>
+        <v>542289</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>100222</t>
+          <t>99462</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>50659.85227632982</t>
+          <t>54207.46786489506</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>113010.0728918695</t>
+          <t>73719.35360200389</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>712499.0</t>
+          <t>417886.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>202.87</t>
+          <t>189.10</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1278,17 +1278,17 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>67.01</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>827.0</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>835.0</t>
+          <t>776.0</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>754.0</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>792.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1382.0</t>
+          <t>878.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>811.0</t>
+          <t>792.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.20</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>43.17</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,66 +1556,66 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.05</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>6.74</v>
+        <v>2.43</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.22</v>
+        <v>12.38</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>759.8</t>
+          <t>773.2</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>683.15</v>
+        <v>688.05</v>
       </c>
       <c r="AV3" t="n">
-        <v>756.38</v>
+        <v>755.04</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>720.9</t>
+          <t>724.66</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>290.80</t>
+          <t>917.69</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>13.42</v>
+        <v>17.46</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-7.04</v>
+        <v>-2.14</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-102.37</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>428295.7451923077</t>
+          <t>428930.0367412141</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>1121228.0</t>
+          <t>712499.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>834088.6</v>
+        <v>795957</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>640629.9</t>
+          <t>695734.8</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>559003.52</v>
+        <v>555261.3199999999</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>193458</t>
+          <t>100222</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>39323.44852804988</t>
+          <t>50659.85227632982</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>133537.9192741107</t>
+          <t>113010.0728918695</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1121228.0</t>
+          <t>712499.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>210.13</t>
+          <t>202.87</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,22 +1735,22 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>67.01</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>827.0</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>838.0</t>
+          <t>835.0</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>781.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>811.0</t>
+          <t>792.0</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1893.0</t>
+          <t>1382.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>811.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.83</t>
+          <t>30.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,12 +2018,12 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2033,51 +2033,51 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>89.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>4.65</v>
+        <v>6.74</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.36</v>
+        <v>11.22</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>748.2</t>
+          <t>759.8</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>677.95</v>
+        <v>683.15</v>
       </c>
       <c r="AV4" t="n">
-        <v>758.04</v>
+        <v>756.38</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>716.71</t>
+          <t>720.9</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>150.52</t>
+          <t>290.80</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>6.14</v>
+        <v>13.42</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-12.15</v>
+        <v>-7.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-113.51</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>428295.7451923077</t>
+          <t>428930.0367412141</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>1507537.0</t>
+          <t>1121228.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>875611.4</v>
+        <v>834088.6</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>544437.3</t>
+          <t>640629.9</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>555489.76</v>
+        <v>559003.52</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>331174</t>
+          <t>193458</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>22193.54475603881</t>
+          <t>39323.44852804988</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>114301.8098460946</t>
+          <t>133537.9192741107</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1507537.0</t>
+          <t>1121228.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>199.43</t>
+          <t>210.13</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>67.01</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>779.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>829.0</t>
+          <t>838.0</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>781.0</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>811.0</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>498.0</t>
+          <t>1893.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.24</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,12 +2480,12 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2495,51 +2495,51 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>89.57</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>3.81</v>
+        <v>4.65</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.98</v>
+        <v>10.36</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-11.21</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>748.2</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>674.45</v>
+        <v>677.95</v>
       </c>
       <c r="AV5" t="n">
-        <v>759.64</v>
+        <v>758.04</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>712.93</t>
+          <t>716.71</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>97.61</t>
+          <t>150.52</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>-0.4</v>
+        <v>6.14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-16.72</v>
+        <v>-12.15</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-118.59</t>
+          <t>-113.51</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>428295.7451923077</t>
+          <t>428930.0367412141</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>365930.0</t>
+          <t>1507537.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>671144.2</v>
+        <v>875611.4</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>403254.7</t>
+          <t>544437.3</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>540261.2</v>
+        <v>555489.76</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>267889</t>
+          <t>331174</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>5446.587466937765</t>
+          <t>22193.54475603881</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>41349.19602585369</t>
+          <t>114301.8098460946</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>365930.0</t>
+          <t>1507537.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>191.78</t>
+          <t>199.43</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2659,22 +2659,22 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>67.01</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>767.0</t>
+          <t>829.0</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>382.0</t>
+          <t>498.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-10.24</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,17 +2942,17 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2961,47 +2961,47 @@
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>0.59</v>
+        <v>3.81</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.95</v>
+        <v>8.98</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-11.73</t>
+          <t>-11.21</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>672.75</v>
+        <v>674.45</v>
       </c>
       <c r="AV6" t="n">
-        <v>762.16</v>
+        <v>759.64</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>709.39</t>
+          <t>712.93</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>97.61</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-6.7</v>
+        <v>-0.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-20.8</v>
+        <v>-16.72</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-123.13</t>
+          <t>-118.59</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>428295.7451923077</t>
+          <t>428930.0367412141</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>626091.6</v>
+        <v>671144.2</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>384772.2</t>
+          <t>403254.7</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>572103.12</v>
+        <v>540261.2</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>241319</t>
+          <t>267889</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-1081.15954377422</t>
+          <t>5446.587466937765</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>57969.45499601483</t>
+          <t>41349.19602585369</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>191.78</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>67.01</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>708.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>724.0</t>
+          <t>767.0</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1188.0</t>
+          <t>382.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.46</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,66 +3404,66 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>91.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>3.75</v>
+        <v>0.59</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.88</v>
+        <v>5.95</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.73</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>672.7</v>
+        <v>672.75</v>
       </c>
       <c r="AV7" t="n">
-        <v>765</v>
+        <v>762.16</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>706.65</t>
+          <t>709.39</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>59.04</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-24.33</v>
+        <v>-20.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-127.05</t>
+          <t>-123.13</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>428295.7451923077</t>
+          <t>428930.0367412141</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>595512.6</v>
+        <v>626091.6</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>371093.3</t>
+          <t>384772.2</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>588379.48</v>
+        <v>572103.12</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>224419</t>
+          <t>241319</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-11817.63491464496</t>
+          <t>-1081.15954377422</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>89642.95156067307</t>
+          <t>57969.45499601483</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>177.25</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,22 +3583,22 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>67.01</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>724.0</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1760.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,66 +3866,66 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>91.88</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>9.960000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.63</v>
+        <v>3.88</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>684.8</t>
+          <t>698.8</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>673.8</v>
+        <v>672.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>766.12</v>
+        <v>765</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>703.69</t>
+          <t>706.65</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>59.04</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>-14.8</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-27.92</v>
+        <v>-24.33</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-131.04</t>
+          <t>-127.05</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>428295.7451923077</t>
+          <t>428930.0367412141</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>447171.2</v>
+        <v>595512.6</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>307005.0</t>
+          <t>371093.3</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>581707.48</v>
+        <v>588379.48</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>140166</t>
+          <t>224419</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-30265.01427379369</t>
+          <t>-11817.63491464496</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>64128.62695444649</t>
+          <t>89642.95156067307</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>187.95</t>
+          <t>177.25</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,22 +4045,22 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.10</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>67.01</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>733.0</t>
+          <t>764.0</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4147,7 +4147,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>696.0</t>
+          <t>1760.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,12 +4328,12 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4343,51 +4343,51 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>91.85</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>8.34</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>661.8</t>
+          <t>684.8</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>674.65</v>
+        <v>673.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>766.6799999999999</v>
+        <v>766.12</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>700.39</t>
+          <t>703.69</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-23.61</v>
+        <v>-14.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-31.2</v>
+        <v>-27.92</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-134.68</t>
+          <t>-131.04</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>428295.7451923077</t>
+          <t>428930.0367412141</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>213263.2</v>
+        <v>447171.2</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>198676.6</t>
+          <t>307005.0</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>573003.24</v>
+        <v>581707.48</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>140166</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-47427.49449711009</t>
+          <t>-30265.01427379369</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-20219.82344567886</t>
+          <t>64128.62695444649</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>187.95</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>67.01</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>733.0</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,17 +4790,17 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4809,47 +4809,47 @@
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>0.87</v>
+        <v>8.34</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-4.26</v>
+        <v>-1.9</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>646.4</t>
+          <t>661.8</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>675.15</v>
+        <v>674.65</v>
       </c>
       <c r="AV10" t="n">
-        <v>766.86</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>697.59</t>
+          <t>700.39</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>-30.84</v>
+        <v>-23.61</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-33.1</v>
+        <v>-31.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-136.79</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>428295.7451923077</t>
+          <t>428930.0367412141</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>135365.2</v>
+        <v>213263.2</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>174307.3</t>
+          <t>198676.6</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>574226.34</v>
+        <v>573003.24</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-38942</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-52374.34377918849</t>
+          <t>-47427.49449711009</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-49605.36603708362</t>
+          <t>-20219.82344567886</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>149.33</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,22 +4969,22 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>67.01</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>644.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,266 +5252,266 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>0.47</v>
+        <v>0.87</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-5.06</v>
+        <v>-4.26</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>-30.84</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>428930.0367412141</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BF11" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="BH11" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>63.96</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>17585</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AU11" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AY11" t="n">
-        <v>-33</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-33.66</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>428295.7451923077</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BF11" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="BH11" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>67.01</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>47.2</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
-        <is>
-          <t>18423</t>
-        </is>
-      </c>
-      <c r="CI11" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CJ11" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CK11" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CL11" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CM11" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CN11" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5533,7 +5533,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,66 +5714,66 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>547</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>2.47</v>
+        <v>0.47</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-6.43</v>
+        <v>-5.06</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AV12" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-34.77</v>
+        <v>-33</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-33.83</v>
+        <v>-33.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>428295.7451923077</t>
+          <t>428930.0367412141</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>67.01</t>
+          <t>63.96</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>-3.84</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>713.0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-3.84</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>17.09</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-2.38</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>547</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>41.49</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>76.51</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>-3.2</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>12.81</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-7.85</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>3.23</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>781.0</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>692.3</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>751.28</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>727.76</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>873.82</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>17.56</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>1.8</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>89.95</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-98.00</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>428930.0367412141</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>417886.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>825016</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>725553.8</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>542289</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>99462</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>54207.46786489506</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>73719.35360200389</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>417886.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>189.10</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價跌量縮</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>19.92</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>63.96</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>17585</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>773.0</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>776.0</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>754.0</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>756.0</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>713.0</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>27.43</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-5.18</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>547</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>88.05</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>96.02</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>2.43</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>12.38</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-8.87</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>4.19</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>773.2</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>688.05</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>755.04</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>724.66</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>917.69</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>17.46</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-2.14</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>89.95</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-102.37</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>428930.0367412141</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>712499.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>795957</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>695734.8</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>555261.3199999999</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>100222</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>50659.85227632982</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>113010.0728918695</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>712499.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>202.87</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價跌量增</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>20.86</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>63.96</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>17585</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>827.0</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>835.0</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>790.0</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>792.0</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>713.0</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>43.17</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>547</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>6.74</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>11.22</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-9.68</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>4.92</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>759.8</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>683.15</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>756.38</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>720.9</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>290.80</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>13.42</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-7.04</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>89.95</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-107.82</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>428930.0367412141</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>1121228.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>834088.6</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>640629.9</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>559003.52</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>193458</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>39323.44852804988</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>133537.9192741107</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>1121228.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>210.13</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>21.36</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>63.96</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>17585</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>804.0</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>838.0</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>781.0</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>811.0</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>713.0</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>59.14</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-4.71</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>547</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>89.57</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>4.65</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>10.36</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-10.57</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>5.77</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>748.2</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>677.95</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>758.04</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>716.71</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>150.52</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>6.14</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-12.15</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>89.95</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-113.51</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>428930.0367412141</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>1507537.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>875611.4</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>544437.3</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>555489.76</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>331174</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>22193.54475603881</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>114301.8098460946</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>1507537.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>199.43</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>20.63</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>63.96</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>17585</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>779.0</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>829.0</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>774.0</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>783.0</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>713.0</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>15.56</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>5.89</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>547</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>81.45</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>3.81</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>8.98</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-11.21</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>6.55</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>735.0</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>674.45</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>759.64</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>712.93</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>97.61</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-16.72</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>89.95</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-118.59</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>428930.0367412141</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>365930.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>671144.2</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>403254.7</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>540261.2</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>267889</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>5446.587466937765</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>41349.19602585369</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>365930.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>191.78</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>20.10</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>63.96</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>17585</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>729.0</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>767.0</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>717.0</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>763.0</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>713.0</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>11.93</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>547</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>68.7</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>81.45</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>0.59</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>5.95</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-11.73</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>7.44</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>712.8</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>672.75</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>762.16</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>709.39</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>67.78</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-6.7</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-20.8</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>89.95</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-123.13</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>428930.0367412141</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>272591.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>626091.6</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>384772.2</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>572103.12</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>241319</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-1081.15954377422</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>57969.45499601483</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>272591.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>174.19</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價跌量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>18.89</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>63.96</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>17585</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>708.0</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>724.0</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>705.0</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>717.0</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>713.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>37.11</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>-8.55</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>547</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>75.65</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>91.88</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>3.88</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-12.07</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>8.26</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>698.8</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>672.7</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>765</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>706.65</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>59.04</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-9.970000000000001</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-24.33</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>89.95</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-127.05</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>428930.0367412141</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>903157.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>595512.6</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>371093.3</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>588379.48</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>224419</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-11817.63491464496</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>89642.95156067307</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>903157.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>177.25</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價跌量增</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>19.10</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>63.96</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>17585</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>764.0</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>790.0</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>722.0</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>725.0</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>5.53</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>713.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>5.53</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>54.98</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.60</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>547</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>97.78</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>1.63</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-12.05</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>8.87</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>684.8</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>673.8</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>766.12</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>703.69</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>46.99</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-14.8</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-27.92</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>89.95</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-131.04</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>428930.0367412141</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>1328842.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>447171.2</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>307005.0</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>581707.48</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>140166</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-30265.01427379369</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>64128.62695444649</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>1328842.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>187.95</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>19.84</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>63.96</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>17585</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>733.0</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>783.0</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>720.0</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>753.0</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>713.0</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>5.33</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>21.74</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>9.47</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>547</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>91.85</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>8.34</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-1.9</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-12.0</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>9.47</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>661.8</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>674.65</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>766.6799999999999</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>700.39</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>24.34</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-23.61</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-31.2</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>89.95</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-134.68</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>428930.0367412141</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>485201.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>213263.2</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>198676.6</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>573003.24</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>14586</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-47427.49449711009</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-20219.82344567886</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>485201.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>174.19</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>18.89</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>63.96</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>17585</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>658.0</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>717.0</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>655.0</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>717.0</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>713.0</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>6.72</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-1.37</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>547</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>93.33</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>91.85</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>0.87</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-4.26</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-11.96</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>9.93</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>646.4</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>675.15</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>766.86</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>697.59</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>6.83</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-30.84</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-33.1</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>89.95</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-136.79</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>428930.0367412141</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>140667.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>135365.2</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>174307.3</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>574226.34</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-38942</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-52374.34377918849</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-49605.36603708362</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>140667.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>149.33</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>17.18</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>63.96</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>17585</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>647.0</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>669.0</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>652.0</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>713.0</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>5.81</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-0.90</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>547</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>82.22</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>76.04</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>0.47</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-5.06</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-11.65</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>10.41</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>678.35</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>767.8200000000001</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>695.44</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>1.96</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-33</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-33.66</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>89.95</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-137.42</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>428930.0367412141</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>119696.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>143452.8</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>198038.4</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>598609.88</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-54585</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-52877.79427775302</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-52898.73523776597</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>119696.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>147.42</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>17.04</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>63.96</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>17585</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>663.0</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>663.0</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>637.0</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>647.0</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>547.0</t>
+          <t>517.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-12.35</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>16.15</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>29.79</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>76.51</t>
+          <t>53.11</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-3.2</v>
+        <v>-4.17</v>
       </c>
       <c r="AU2" t="n">
-        <v>12.81</v>
+        <v>11.5</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>781.0</t>
+          <t>777.4</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>692.3</v>
+        <v>697.25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>751.28</v>
+        <v>746.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>727.76</t>
+          <t>731.1</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>873.82</t>
+          <t>248.27</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>17.56</v>
+        <v>16.55</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.8</v>
+        <v>4.75</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-98.00</t>
+          <t>-94.72</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>428930.0367412141</t>
+          <t>429437.1974522293</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>417886.0</t>
+          <t>392119.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>825016</v>
+        <v>830253.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>725553.8</t>
+          <t>750699.0</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>542289</v>
+        <v>514472.8</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>99462</t>
+          <t>79554</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>54207.46786489506</t>
+          <t>52397.14069476472</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>73719.35360200389</t>
+          <t>42440.34125904785</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>417886.0</t>
+          <t>392119.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>189.10</t>
+          <t>184.89</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>63.03</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>773.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>776.0</t>
+          <t>777.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>754.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>878.0</t>
+          <t>547.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>792.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>13.71</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>88.05</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>96.02</t>
+          <t>76.51</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2.43</v>
+        <v>-3.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>12.38</v>
+        <v>12.81</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>773.2</t>
+          <t>781.0</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>688.05</v>
+        <v>692.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>755.04</v>
+        <v>751.28</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>724.66</t>
+          <t>727.76</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>917.69</t>
+          <t>873.82</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>17.46</v>
+        <v>17.56</v>
       </c>
       <c r="BD3" t="n">
-        <v>-2.14</v>
+        <v>1.8</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-102.37</t>
+          <t>-98.00</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>428930.0367412141</t>
+          <t>429437.1974522293</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>712499.0</t>
+          <t>417886.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>795957</v>
+        <v>825016</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>695734.8</t>
+          <t>725553.8</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>555261.3199999999</v>
+        <v>542289</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>100222</t>
+          <t>99462</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>50659.85227632982</t>
+          <t>54207.46786489506</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>113010.0728918695</t>
+          <t>73719.35360200389</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>712499.0</t>
+          <t>417886.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>202.87</t>
+          <t>189.10</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>63.03</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>827.0</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>835.0</t>
+          <t>776.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>754.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>792.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1382.0</t>
+          <t>878.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>811.0</t>
+          <t>792.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30.20</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>43.17</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>6.74</v>
+        <v>2.43</v>
       </c>
       <c r="AU4" t="n">
-        <v>11.22</v>
+        <v>12.38</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>759.8</t>
+          <t>773.2</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>683.15</v>
+        <v>688.05</v>
       </c>
       <c r="AZ4" t="n">
-        <v>756.38</v>
+        <v>755.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>720.9</t>
+          <t>724.66</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>290.80</t>
+          <t>917.69</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>13.42</v>
+        <v>17.46</v>
       </c>
       <c r="BD4" t="n">
-        <v>-7.04</v>
+        <v>-2.14</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-102.37</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>428930.0367412141</t>
+          <t>429437.1974522293</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>1121228.0</t>
+          <t>712499.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>834088.6</v>
+        <v>795957</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>640629.9</t>
+          <t>695734.8</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>559003.52</v>
+        <v>555261.3199999999</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>193458</t>
+          <t>100222</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>39323.44852804988</t>
+          <t>50659.85227632982</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>133537.9192741107</t>
+          <t>113010.0728918695</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>1121228.0</t>
+          <t>712499.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>210.13</t>
+          <t>202.87</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>63.03</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>827.0</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>838.0</t>
+          <t>835.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>781.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>811.0</t>
+          <t>792.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1893.0</t>
+          <t>1382.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>811.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>60.83</t>
+          <t>30.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2595,51 +2595,51 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>89.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>4.65</v>
+        <v>6.74</v>
       </c>
       <c r="AU5" t="n">
-        <v>10.36</v>
+        <v>11.22</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>748.2</t>
+          <t>759.8</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>677.95</v>
+        <v>683.15</v>
       </c>
       <c r="AZ5" t="n">
-        <v>758.04</v>
+        <v>756.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>716.71</t>
+          <t>720.9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>150.52</t>
+          <t>290.80</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>6.14</v>
+        <v>13.42</v>
       </c>
       <c r="BD5" t="n">
-        <v>-12.15</v>
+        <v>-7.04</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-113.51</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>428930.0367412141</t>
+          <t>429437.1974522293</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>1507537.0</t>
+          <t>1121228.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>875611.4</v>
+        <v>834088.6</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>544437.3</t>
+          <t>640629.9</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>555489.76</v>
+        <v>559003.52</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>331174</t>
+          <t>193458</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>22193.54475603881</t>
+          <t>39323.44852804988</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>114301.8098460946</t>
+          <t>133537.9192741107</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1507537.0</t>
+          <t>1121228.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>199.43</t>
+          <t>210.13</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>63.03</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>779.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>829.0</t>
+          <t>838.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>781.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>811.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>498.0</t>
+          <t>1893.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.24</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,12 +3062,12 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3077,51 +3077,51 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>89.57</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>3.81</v>
+        <v>4.65</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.98</v>
+        <v>10.36</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-11.21</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>748.2</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>674.45</v>
+        <v>677.95</v>
       </c>
       <c r="AZ6" t="n">
-        <v>759.64</v>
+        <v>758.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>712.93</t>
+          <t>716.71</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>97.61</t>
+          <t>150.52</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.4</v>
+        <v>6.14</v>
       </c>
       <c r="BD6" t="n">
-        <v>-16.72</v>
+        <v>-12.15</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-118.59</t>
+          <t>-113.51</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>428930.0367412141</t>
+          <t>429437.1974522293</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>365930.0</t>
+          <t>1507537.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>671144.2</v>
+        <v>875611.4</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>403254.7</t>
+          <t>544437.3</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>540261.2</v>
+        <v>555489.76</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>267889</t>
+          <t>331174</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>5446.587466937765</t>
+          <t>22193.54475603881</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>41349.19602585369</t>
+          <t>114301.8098460946</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>365930.0</t>
+          <t>1507537.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>191.78</t>
+          <t>199.43</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>63.03</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>767.0</t>
+          <t>829.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>382.0</t>
+          <t>498.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-10.24</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,17 +3544,17 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3563,47 +3563,47 @@
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.59</v>
+        <v>3.81</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.95</v>
+        <v>8.98</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-11.73</t>
+          <t>-11.21</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>672.75</v>
+        <v>674.45</v>
       </c>
       <c r="AZ7" t="n">
-        <v>762.16</v>
+        <v>759.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>709.39</t>
+          <t>712.93</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>97.61</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-6.7</v>
+        <v>-0.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>-20.8</v>
+        <v>-16.72</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-123.13</t>
+          <t>-118.59</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>428930.0367412141</t>
+          <t>429437.1974522293</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>626091.6</v>
+        <v>671144.2</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>384772.2</t>
+          <t>403254.7</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>572103.12</v>
+        <v>540261.2</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>241319</t>
+          <t>267889</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1081.15954377422</t>
+          <t>5446.587466937765</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>57969.45499601483</t>
+          <t>41349.19602585369</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>191.78</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3728,17 +3728,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>63.03</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>708.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>724.0</t>
+          <t>767.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1188.0</t>
+          <t>382.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>91.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>3.75</v>
+        <v>0.59</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.88</v>
+        <v>5.95</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.73</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>672.7</v>
+        <v>672.75</v>
       </c>
       <c r="AZ8" t="n">
-        <v>765</v>
+        <v>762.16</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>706.65</t>
+          <t>709.39</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>59.04</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>-24.33</v>
+        <v>-20.8</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-127.05</t>
+          <t>-123.13</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>428930.0367412141</t>
+          <t>429437.1974522293</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>595512.6</v>
+        <v>626091.6</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>371093.3</t>
+          <t>384772.2</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>588379.48</v>
+        <v>572103.12</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>224419</t>
+          <t>241319</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-11817.63491464496</t>
+          <t>-1081.15954377422</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>89642.95156067307</t>
+          <t>57969.45499601483</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>177.25</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>63.03</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>724.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1760.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>91.88</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>9.960000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.63</v>
+        <v>3.88</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>684.8</t>
+          <t>698.8</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>673.8</v>
+        <v>672.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>766.12</v>
+        <v>765</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>703.69</t>
+          <t>706.65</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>59.04</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-14.8</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="BD9" t="n">
-        <v>-27.92</v>
+        <v>-24.33</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-131.04</t>
+          <t>-127.05</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>428930.0367412141</t>
+          <t>429437.1974522293</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>447171.2</v>
+        <v>595512.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>307005.0</t>
+          <t>371093.3</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>581707.48</v>
+        <v>588379.48</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>140166</t>
+          <t>224419</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-30265.01427379369</t>
+          <t>-11817.63491464496</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>64128.62695444649</t>
+          <t>89642.95156067307</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>187.95</t>
+          <t>177.25</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.10</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>63.03</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>733.0</t>
+          <t>764.0</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4789,7 +4789,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>696.0</t>
+          <t>1760.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,12 +4990,12 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5005,51 +5005,51 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>91.85</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>8.34</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>-1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>661.8</t>
+          <t>684.8</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>674.65</v>
+        <v>673.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>766.6799999999999</v>
+        <v>766.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>700.39</t>
+          <t>703.69</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-23.61</v>
+        <v>-14.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>-31.2</v>
+        <v>-27.92</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-134.68</t>
+          <t>-131.04</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>428930.0367412141</t>
+          <t>429437.1974522293</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>213263.2</v>
+        <v>447171.2</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>198676.6</t>
+          <t>307005.0</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>573003.24</v>
+        <v>581707.48</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>140166</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-47427.49449711009</t>
+          <t>-30265.01427379369</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-20219.82344567886</t>
+          <t>64128.62695444649</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>187.95</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>63.03</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>733.0</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,17 +5472,17 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5491,47 +5491,47 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.87</v>
+        <v>8.34</v>
       </c>
       <c r="AU11" t="n">
-        <v>-4.26</v>
+        <v>-1.9</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>646.4</t>
+          <t>661.8</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>675.15</v>
+        <v>674.65</v>
       </c>
       <c r="AZ11" t="n">
-        <v>766.86</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>697.59</t>
+          <t>700.39</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-30.84</v>
+        <v>-23.61</v>
       </c>
       <c r="BD11" t="n">
-        <v>-33.1</v>
+        <v>-31.2</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-136.79</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>428930.0367412141</t>
+          <t>429437.1974522293</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>135365.2</v>
+        <v>213263.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>174307.3</t>
+          <t>198676.6</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>574226.34</v>
+        <v>573003.24</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-38942</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-52374.34377918849</t>
+          <t>-47427.49449711009</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-49605.36603708362</t>
+          <t>-20219.82344567886</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>149.33</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>63.96</t>
+          <t>63.03</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>644.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>12.48</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,266 +5954,266 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.47</v>
+        <v>0.87</v>
       </c>
       <c r="AU12" t="n">
-        <v>-5.06</v>
+        <v>-4.26</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>-30.84</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>429437.1974522293</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="BL12" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>63.03</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>46.96</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>17329</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AY12" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-33</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-33.66</v>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>428930.0367412141</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BJ12" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="BL12" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="CH12" t="inlineStr">
-        <is>
-          <t>63.96</t>
-        </is>
-      </c>
-      <c r="CI12" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="CJ12" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="CK12" t="inlineStr">
-        <is>
-          <t>47.76</t>
-        </is>
-      </c>
-      <c r="CL12" t="inlineStr">
-        <is>
-          <t>17585</t>
-        </is>
-      </c>
-      <c r="CM12" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN12" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CO12" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CP12" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CQ12" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>517.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>-18.00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.35</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>53.11</t>
+          <t>23.76</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-4.17</v>
+        <v>-6.18</v>
       </c>
       <c r="AU2" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>777.4</t>
+          <t>764.2</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>697.25</v>
+        <v>701.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>746.76</v>
+        <v>741.12</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>731.1</t>
+          <t>733.5</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>248.27</t>
+          <t>106.21</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>16.55</v>
+        <v>13.35</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.75</v>
+        <v>6.47</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-94.72</t>
+          <t>-92.81</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>429437.1974522293</t>
+          <t>429972.180952381</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>392119.0</t>
+          <t>398638.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>830253.8</v>
+        <v>608474</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>750699.0</t>
+          <t>742042.7</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>514472.8</v>
+        <v>503291.98</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>-133568</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>52397.14069476472</t>
+          <t>47408.80352441666</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>42440.34125904785</t>
+          <t>19972.94908750232</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>392119.0</t>
+          <t>398638.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>184.89</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>63.03</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>777.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>547.0</t>
+          <t>517.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-12.35</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>16.15</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>29.79</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>76.51</t>
+          <t>53.11</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-3.2</v>
+        <v>-4.17</v>
       </c>
       <c r="AU3" t="n">
-        <v>12.81</v>
+        <v>11.5</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>781.0</t>
+          <t>777.4</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>692.3</v>
+        <v>697.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>751.28</v>
+        <v>746.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>727.76</t>
+          <t>731.1</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>873.82</t>
+          <t>248.27</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>17.56</v>
+        <v>16.55</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.8</v>
+        <v>4.75</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-98.00</t>
+          <t>-94.72</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>429437.1974522293</t>
+          <t>429972.180952381</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>417886.0</t>
+          <t>392119.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>825016</v>
+        <v>830253.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>725553.8</t>
+          <t>750699.0</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>542289</v>
+        <v>514472.8</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>99462</t>
+          <t>79554</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>54207.46786489506</t>
+          <t>52397.14069476472</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>73719.35360200389</t>
+          <t>42440.34125904785</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>417886.0</t>
+          <t>392119.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>189.10</t>
+          <t>184.89</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>63.03</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>773.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>776.0</t>
+          <t>777.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>754.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>878.0</t>
+          <t>547.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>792.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>13.71</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>88.05</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>96.02</t>
+          <t>76.51</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>2.43</v>
+        <v>-3.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>12.38</v>
+        <v>12.81</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>773.2</t>
+          <t>781.0</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>688.05</v>
+        <v>692.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>755.04</v>
+        <v>751.28</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>724.66</t>
+          <t>727.76</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>917.69</t>
+          <t>873.82</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>17.46</v>
+        <v>17.56</v>
       </c>
       <c r="BD4" t="n">
-        <v>-2.14</v>
+        <v>1.8</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-102.37</t>
+          <t>-98.00</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>429437.1974522293</t>
+          <t>429972.180952381</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>712499.0</t>
+          <t>417886.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>795957</v>
+        <v>825016</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>695734.8</t>
+          <t>725553.8</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>555261.3199999999</v>
+        <v>542289</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>100222</t>
+          <t>99462</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>50659.85227632982</t>
+          <t>54207.46786489506</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>113010.0728918695</t>
+          <t>73719.35360200389</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>712499.0</t>
+          <t>417886.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>202.87</t>
+          <t>189.10</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2282,17 +2282,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>63.03</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>827.0</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>835.0</t>
+          <t>776.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>754.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>792.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1382.0</t>
+          <t>878.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>811.0</t>
+          <t>792.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.20</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.17</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>6.74</v>
+        <v>2.43</v>
       </c>
       <c r="AU5" t="n">
-        <v>11.22</v>
+        <v>12.38</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>759.8</t>
+          <t>773.2</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>683.15</v>
+        <v>688.05</v>
       </c>
       <c r="AZ5" t="n">
-        <v>756.38</v>
+        <v>755.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>720.9</t>
+          <t>724.66</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>290.80</t>
+          <t>917.69</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>13.42</v>
+        <v>17.46</v>
       </c>
       <c r="BD5" t="n">
-        <v>-7.04</v>
+        <v>-2.14</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-102.37</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>429437.1974522293</t>
+          <t>429972.180952381</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>1121228.0</t>
+          <t>712499.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>834088.6</v>
+        <v>795957</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>640629.9</t>
+          <t>695734.8</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>559003.52</v>
+        <v>555261.3199999999</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>193458</t>
+          <t>100222</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>39323.44852804988</t>
+          <t>50659.85227632982</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>133537.9192741107</t>
+          <t>113010.0728918695</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1121228.0</t>
+          <t>712499.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>210.13</t>
+          <t>202.87</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>63.03</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>827.0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>838.0</t>
+          <t>835.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>781.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>811.0</t>
+          <t>792.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1893.0</t>
+          <t>1382.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>811.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>60.83</t>
+          <t>30.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,12 +3062,12 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3077,51 +3077,51 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>89.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>4.65</v>
+        <v>6.74</v>
       </c>
       <c r="AU6" t="n">
-        <v>10.36</v>
+        <v>11.22</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>748.2</t>
+          <t>759.8</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>677.95</v>
+        <v>683.15</v>
       </c>
       <c r="AZ6" t="n">
-        <v>758.04</v>
+        <v>756.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>716.71</t>
+          <t>720.9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>150.52</t>
+          <t>290.80</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>6.14</v>
+        <v>13.42</v>
       </c>
       <c r="BD6" t="n">
-        <v>-12.15</v>
+        <v>-7.04</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-113.51</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>429437.1974522293</t>
+          <t>429972.180952381</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>1507537.0</t>
+          <t>1121228.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>875611.4</v>
+        <v>834088.6</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>544437.3</t>
+          <t>640629.9</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>555489.76</v>
+        <v>559003.52</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>331174</t>
+          <t>193458</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>22193.54475603881</t>
+          <t>39323.44852804988</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>114301.8098460946</t>
+          <t>133537.9192741107</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>1507537.0</t>
+          <t>1121228.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>199.43</t>
+          <t>210.13</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>63.03</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>779.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>829.0</t>
+          <t>838.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>781.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>811.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>498.0</t>
+          <t>1893.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-9.21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.24</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,12 +3544,12 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3559,51 +3559,51 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>89.57</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>3.81</v>
+        <v>4.65</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.98</v>
+        <v>10.36</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-11.21</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>748.2</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>674.45</v>
+        <v>677.95</v>
       </c>
       <c r="AZ7" t="n">
-        <v>759.64</v>
+        <v>758.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>712.93</t>
+          <t>716.71</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>97.61</t>
+          <t>150.52</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.4</v>
+        <v>6.14</v>
       </c>
       <c r="BD7" t="n">
-        <v>-16.72</v>
+        <v>-12.15</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-118.59</t>
+          <t>-113.51</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>429437.1974522293</t>
+          <t>429972.180952381</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>365930.0</t>
+          <t>1507537.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>671144.2</v>
+        <v>875611.4</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>403254.7</t>
+          <t>544437.3</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>540261.2</v>
+        <v>555489.76</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>267889</t>
+          <t>331174</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>5446.587466937765</t>
+          <t>22193.54475603881</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>41349.19602585369</t>
+          <t>114301.8098460946</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>365930.0</t>
+          <t>1507537.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>191.78</t>
+          <t>199.43</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,22 +3723,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>63.03</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>767.0</t>
+          <t>829.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>382.0</t>
+          <t>498.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-10.24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4045,47 +4045,47 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>0.59</v>
+        <v>3.81</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.95</v>
+        <v>8.98</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-11.73</t>
+          <t>-11.21</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>672.75</v>
+        <v>674.45</v>
       </c>
       <c r="AZ8" t="n">
-        <v>762.16</v>
+        <v>759.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>709.39</t>
+          <t>712.93</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>97.61</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-6.7</v>
+        <v>-0.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>-20.8</v>
+        <v>-16.72</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-123.13</t>
+          <t>-118.59</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>429437.1974522293</t>
+          <t>429972.180952381</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>626091.6</v>
+        <v>671144.2</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>384772.2</t>
+          <t>403254.7</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>572103.12</v>
+        <v>540261.2</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>241319</t>
+          <t>267889</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-1081.15954377422</t>
+          <t>5446.587466937765</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>57969.45499601483</t>
+          <t>41349.19602585369</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>191.78</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>63.03</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>708.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>724.0</t>
+          <t>767.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1188.0</t>
+          <t>382.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>91.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>3.75</v>
+        <v>0.59</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.88</v>
+        <v>5.95</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.73</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>672.7</v>
+        <v>672.75</v>
       </c>
       <c r="AZ9" t="n">
-        <v>765</v>
+        <v>762.16</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>706.65</t>
+          <t>709.39</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>59.04</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.7</v>
       </c>
       <c r="BD9" t="n">
-        <v>-24.33</v>
+        <v>-20.8</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-127.05</t>
+          <t>-123.13</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>429437.1974522293</t>
+          <t>429972.180952381</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>595512.6</v>
+        <v>626091.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>371093.3</t>
+          <t>384772.2</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>588379.48</v>
+        <v>572103.12</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>224419</t>
+          <t>241319</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-11817.63491464496</t>
+          <t>-1081.15954377422</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>89642.95156067307</t>
+          <t>57969.45499601483</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>177.25</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>63.03</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>724.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1760.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>91.88</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>9.960000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.63</v>
+        <v>3.88</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>684.8</t>
+          <t>698.8</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>673.8</v>
+        <v>672.7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>766.12</v>
+        <v>765</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>703.69</t>
+          <t>706.65</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>59.04</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-14.8</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="BD10" t="n">
-        <v>-27.92</v>
+        <v>-24.33</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-131.04</t>
+          <t>-127.05</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>429437.1974522293</t>
+          <t>429972.180952381</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>447171.2</v>
+        <v>595512.6</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>307005.0</t>
+          <t>371093.3</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>581707.48</v>
+        <v>588379.48</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>140166</t>
+          <t>224419</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-30265.01427379369</t>
+          <t>-11817.63491464496</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>64128.62695444649</t>
+          <t>89642.95156067307</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>187.95</t>
+          <t>177.25</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.10</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>63.03</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>733.0</t>
+          <t>764.0</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>696.0</t>
+          <t>1760.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,12 +5472,12 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5487,51 +5487,51 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>91.85</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>8.34</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>-1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>661.8</t>
+          <t>684.8</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>674.65</v>
+        <v>673.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>766.6799999999999</v>
+        <v>766.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>700.39</t>
+          <t>703.69</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-23.61</v>
+        <v>-14.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>-31.2</v>
+        <v>-27.92</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-134.68</t>
+          <t>-131.04</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>429437.1974522293</t>
+          <t>429972.180952381</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>213263.2</v>
+        <v>447171.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>198676.6</t>
+          <t>307005.0</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>573003.24</v>
+        <v>581707.48</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>140166</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-47427.49449711009</t>
+          <t>-30265.01427379369</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-20219.82344567886</t>
+          <t>64128.62695444649</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>187.95</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>63.03</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>733.0</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,17 +5954,17 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5973,47 +5973,47 @@
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.87</v>
+        <v>8.34</v>
       </c>
       <c r="AU12" t="n">
-        <v>-4.26</v>
+        <v>-1.9</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>646.4</t>
+          <t>661.8</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>675.15</v>
+        <v>674.65</v>
       </c>
       <c r="AZ12" t="n">
-        <v>766.86</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>697.59</t>
+          <t>700.39</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-30.84</v>
+        <v>-23.61</v>
       </c>
       <c r="BD12" t="n">
-        <v>-33.1</v>
+        <v>-31.2</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-136.79</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>429437.1974522293</t>
+          <t>429972.180952381</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>135365.2</v>
+        <v>213263.2</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>174307.3</t>
+          <t>198676.6</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>574226.34</v>
+        <v>573003.24</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-38942</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-52374.34377918849</t>
+          <t>-47427.49449711009</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-49605.36603708362</t>
+          <t>-20219.82344567886</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>149.33</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>63.03</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>644.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/AGV及AMR.xlsx
+++ b/Result/checksun_type/AGV及AMR.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.00</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-16.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1149,51 +1149,51 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>23.76</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-6.18</v>
+        <v>-5.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>9</v>
+        <v>5.49</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>764.2</t>
+          <t>743.2</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>701.1</v>
+        <v>704.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>741.12</v>
+        <v>735.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>733.5</t>
+          <t>735.11</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>106.21</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>13.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.47</v>
+        <v>7.14</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-92.81</t>
+          <t>-92.07</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>429972.180952381</t>
+          <t>429459.0047468354</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>398638.0</t>
+          <t>178539.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>608474</v>
+        <v>419936.2</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>742042.7</t>
+          <t>627012.4</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>503291.98</v>
+        <v>493226.58</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-133568</t>
+          <t>-207076</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>47408.80352441666</t>
+          <t>38151.91464992685</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>19972.94908750232</t>
+          <t>-12760.97415976709</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>398638.0</t>
+          <t>178539.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>169.98</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.60</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>726.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>517.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>-18.00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.35</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>53.11</t>
+          <t>23.76</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-4.17</v>
+        <v>-6.18</v>
       </c>
       <c r="AU3" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>777.4</t>
+          <t>764.2</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>697.25</v>
+        <v>701.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>746.76</v>
+        <v>741.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>731.1</t>
+          <t>733.5</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>248.27</t>
+          <t>106.21</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>16.55</v>
+        <v>13.35</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.75</v>
+        <v>6.47</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-94.72</t>
+          <t>-92.81</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>429972.180952381</t>
+          <t>429459.0047468354</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>392119.0</t>
+          <t>398638.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>830253.8</v>
+        <v>608474</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>750699.0</t>
+          <t>742042.7</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>514472.8</v>
+        <v>503291.98</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>-133568</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>52397.14069476472</t>
+          <t>47408.80352441666</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>42440.34125904785</t>
+          <t>19972.94908750232</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>392119.0</t>
+          <t>398638.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>184.89</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>777.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>547.0</t>
+          <t>517.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-12.35</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>16.15</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>29.79</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>76.51</t>
+          <t>53.11</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-3.2</v>
+        <v>-4.17</v>
       </c>
       <c r="AU4" t="n">
-        <v>12.81</v>
+        <v>11.5</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>781.0</t>
+          <t>777.4</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>692.3</v>
+        <v>697.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>751.28</v>
+        <v>746.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>727.76</t>
+          <t>731.1</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>873.82</t>
+          <t>248.27</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>17.56</v>
+        <v>16.55</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.8</v>
+        <v>4.75</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-98.00</t>
+          <t>-94.72</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>429972.180952381</t>
+          <t>429459.0047468354</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>417886.0</t>
+          <t>392119.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>825016</v>
+        <v>830253.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>725553.8</t>
+          <t>750699.0</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>542289</v>
+        <v>514472.8</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>99462</t>
+          <t>79554</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>54207.46786489506</t>
+          <t>52397.14069476472</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>73719.35360200389</t>
+          <t>42440.34125904785</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>417886.0</t>
+          <t>392119.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>189.10</t>
+          <t>184.89</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>773.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>776.0</t>
+          <t>777.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>754.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>878.0</t>
+          <t>547.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>792.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>13.71</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>88.05</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>96.02</t>
+          <t>76.51</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>2.43</v>
+        <v>-3.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>12.38</v>
+        <v>12.81</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>773.2</t>
+          <t>781.0</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>688.05</v>
+        <v>692.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>755.04</v>
+        <v>751.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>724.66</t>
+          <t>727.76</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>917.69</t>
+          <t>873.82</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>17.46</v>
+        <v>17.56</v>
       </c>
       <c r="BD5" t="n">
-        <v>-2.14</v>
+        <v>1.8</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-102.37</t>
+          <t>-98.00</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>429972.180952381</t>
+          <t>429459.0047468354</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>712499.0</t>
+          <t>417886.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>795957</v>
+        <v>825016</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>695734.8</t>
+          <t>725553.8</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>555261.3199999999</v>
+        <v>542289</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>100222</t>
+          <t>99462</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>50659.85227632982</t>
+          <t>54207.46786489506</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>113010.0728918695</t>
+          <t>73719.35360200389</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>712499.0</t>
+          <t>417886.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>202.87</t>
+          <t>189.10</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>827.0</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>835.0</t>
+          <t>776.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>754.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>792.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1382.0</t>
+          <t>878.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>811.0</t>
+          <t>792.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-12.18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>30.20</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.17</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.05</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>6.74</v>
+        <v>2.43</v>
       </c>
       <c r="AU6" t="n">
-        <v>11.22</v>
+        <v>12.38</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>759.8</t>
+          <t>773.2</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>683.15</v>
+        <v>688.05</v>
       </c>
       <c r="AZ6" t="n">
-        <v>756.38</v>
+        <v>755.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>720.9</t>
+          <t>724.66</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>290.80</t>
+          <t>917.69</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>13.42</v>
+        <v>17.46</v>
       </c>
       <c r="BD6" t="n">
-        <v>-7.04</v>
+        <v>-2.14</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-102.37</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>429972.180952381</t>
+          <t>429459.0047468354</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>1121228.0</t>
+          <t>712499.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>834088.6</v>
+        <v>795957</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>640629.9</t>
+          <t>695734.8</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>559003.52</v>
+        <v>555261.3199999999</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>193458</t>
+          <t>100222</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>39323.44852804988</t>
+          <t>50659.85227632982</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>133537.9192741107</t>
+          <t>113010.0728918695</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>1121228.0</t>
+          <t>712499.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>210.13</t>
+          <t>202.87</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>827.0</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>838.0</t>
+          <t>835.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>781.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>811.0</t>
+          <t>792.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1893.0</t>
+          <t>1382.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>811.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-9.21</t>
+          <t>-14.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>60.83</t>
+          <t>30.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,12 +3544,12 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3559,51 +3559,51 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>89.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>4.65</v>
+        <v>6.74</v>
       </c>
       <c r="AU7" t="n">
-        <v>10.36</v>
+        <v>11.22</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>748.2</t>
+          <t>759.8</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>677.95</v>
+        <v>683.15</v>
       </c>
       <c r="AZ7" t="n">
-        <v>758.04</v>
+        <v>756.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>716.71</t>
+          <t>720.9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>150.52</t>
+          <t>290.80</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>6.14</v>
+        <v>13.42</v>
       </c>
       <c r="BD7" t="n">
-        <v>-12.15</v>
+        <v>-7.04</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-113.51</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>429972.180952381</t>
+          <t>429459.0047468354</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>1507537.0</t>
+          <t>1121228.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>875611.4</v>
+        <v>834088.6</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>544437.3</t>
+          <t>640629.9</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>555489.76</v>
+        <v>559003.52</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>331174</t>
+          <t>193458</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>22193.54475603881</t>
+          <t>39323.44852804988</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>114301.8098460946</t>
+          <t>133537.9192741107</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>1507537.0</t>
+          <t>1121228.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>199.43</t>
+          <t>210.13</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>779.0</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>829.0</t>
+          <t>838.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>781.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>811.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>498.0</t>
+          <t>1893.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.24</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4041,51 +4041,51 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>89.57</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>3.81</v>
+        <v>4.65</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.98</v>
+        <v>10.36</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-11.21</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>748.2</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>674.45</v>
+        <v>677.95</v>
       </c>
       <c r="AZ8" t="n">
-        <v>759.64</v>
+        <v>758.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>712.93</t>
+          <t>716.71</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>97.61</t>
+          <t>150.52</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.4</v>
+        <v>6.14</v>
       </c>
       <c r="BD8" t="n">
-        <v>-16.72</v>
+        <v>-12.15</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-118.59</t>
+          <t>-113.51</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>429972.180952381</t>
+          <t>429459.0047468354</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>365930.0</t>
+          <t>1507537.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>671144.2</v>
+        <v>875611.4</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>403254.7</t>
+          <t>544437.3</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>540261.2</v>
+        <v>555489.76</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>267889</t>
+          <t>331174</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>5446.587466937765</t>
+          <t>22193.54475603881</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>41349.19602585369</t>
+          <t>114301.8098460946</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>365930.0</t>
+          <t>1507537.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>191.78</t>
+          <t>199.43</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>767.0</t>
+          <t>829.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>382.0</t>
+          <t>498.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>66.43</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-10.24</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,17 +4508,17 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4527,47 +4527,47 @@
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.59</v>
+        <v>3.81</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.95</v>
+        <v>8.98</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-11.73</t>
+          <t>-11.21</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>672.75</v>
+        <v>674.45</v>
       </c>
       <c r="AZ9" t="n">
-        <v>762.16</v>
+        <v>759.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>709.39</t>
+          <t>712.93</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>97.61</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-6.7</v>
+        <v>-0.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>-20.8</v>
+        <v>-16.72</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-123.13</t>
+          <t>-118.59</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>429972.180952381</t>
+          <t>429459.0047468354</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>626091.6</v>
+        <v>671144.2</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>384772.2</t>
+          <t>403254.7</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>572103.12</v>
+        <v>540261.2</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>241319</t>
+          <t>267889</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-1081.15954377422</t>
+          <t>5446.587466937765</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>57969.45499601483</t>
+          <t>41349.19602585369</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>272591.0</t>
+          <t>365930.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>191.78</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4692,17 +4692,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>708.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>724.0</t>
+          <t>767.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1188.0</t>
+          <t>382.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,162 +4824,162 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>62.72</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>657.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>525.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-15.65</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>9.87</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024/11/25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>192.5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>713.0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>11.93</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
           <t>0.73</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>657.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>850.0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>525.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>598.0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-14.71</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>9.87</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024/11/25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>192.5</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>713.0</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025/04/01</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>220.0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>850.0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2025/09/05</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>598.0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>37.11</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>-8.55</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>91.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>3.75</v>
+        <v>0.59</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.88</v>
+        <v>5.95</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.73</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>672.7</v>
+        <v>672.75</v>
       </c>
       <c r="AZ10" t="n">
-        <v>765</v>
+        <v>762.16</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>706.65</t>
+          <t>709.39</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>59.04</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>-24.33</v>
+        <v>-20.8</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-127.05</t>
+          <t>-123.13</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>429972.180952381</t>
+          <t>429459.0047468354</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>595512.6</v>
+        <v>626091.6</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>371093.3</t>
+          <t>384772.2</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>588379.48</v>
+        <v>572103.12</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>224419</t>
+          <t>241319</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-11817.63491464496</t>
+          <t>-1081.15954377422</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>89642.95156067307</t>
+          <t>57969.45499601483</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>177.25</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,22 +5169,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>724.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="CV10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1760.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>91.88</t>
         </is>
       </c>
       <c r="AT11" t="n">
